--- a/research/traditional_assets/database/data/spain/spain_entertainment.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_entertainment.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1115746061094587</v>
+        <v>0.111329419594185</v>
       </c>
       <c r="C2">
-        <v>149.4099604398442</v>
+        <v>148.408234004589</v>
       </c>
       <c r="D2">
-        <v>144.9299604398443</v>
+        <v>145.472234004589</v>
       </c>
       <c r="E2">
-        <v>-38</v>
+        <v>-36.456</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.544</v>
       </c>
       <c r="G2">
         <v>4.48</v>
@@ -1445,28 +1445,28 @@
         <v>16.28</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0776632</v>
       </c>
       <c r="N2">
-        <v>16.28</v>
+        <v>16.2023368</v>
       </c>
       <c r="O2">
-        <v>4.07</v>
+        <v>4.0505842</v>
       </c>
       <c r="P2">
-        <v>12.21</v>
+        <v>12.1517526</v>
       </c>
       <c r="Q2">
-        <v>15.63</v>
+        <v>15.5717526</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1115746061094587</v>
+        <v>0.1120728985799849</v>
       </c>
       <c r="T2">
-        <v>1.017512237681883</v>
+        <v>1.025220663724927</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>209.6230904727078</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.111329419594185</v>
+        <v>0.1110842330789114</v>
       </c>
       <c r="C3">
-        <v>148.408234004589</v>
+        <v>147.4105807784194</v>
       </c>
       <c r="D3">
-        <v>145.472234004589</v>
+        <v>146.0185807784194</v>
       </c>
       <c r="E3">
-        <v>-36.456</v>
+        <v>-34.912</v>
       </c>
       <c r="F3">
-        <v>1.544</v>
+        <v>3.088</v>
       </c>
       <c r="G3">
         <v>4.48</v>
@@ -1527,28 +1527,28 @@
         <v>16.28</v>
       </c>
       <c r="M3">
-        <v>0.0776632</v>
+        <v>0.1553264</v>
       </c>
       <c r="N3">
-        <v>16.2023368</v>
+        <v>16.1246736</v>
       </c>
       <c r="O3">
-        <v>4.0505842</v>
+        <v>4.0311684</v>
       </c>
       <c r="P3">
-        <v>12.1517526</v>
+        <v>12.0935052</v>
       </c>
       <c r="Q3">
-        <v>15.5717526</v>
+        <v>15.5135052</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1120728985799849</v>
+        <v>0.1125813602846035</v>
       </c>
       <c r="T3">
-        <v>1.025220663724927</v>
+        <v>1.033086404585177</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>209.6230904727078</v>
+        <v>104.8115452363539</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1110842330789114</v>
+        <v>0.1108390465636378</v>
       </c>
       <c r="C4">
-        <v>147.4105807784194</v>
+        <v>146.4170468273218</v>
       </c>
       <c r="D4">
-        <v>146.0185807784194</v>
+        <v>146.5690468273218</v>
       </c>
       <c r="E4">
-        <v>-34.912</v>
+        <v>-33.368</v>
       </c>
       <c r="F4">
-        <v>3.088</v>
+        <v>4.632</v>
       </c>
       <c r="G4">
         <v>4.48</v>
@@ -1609,28 +1609,28 @@
         <v>16.28</v>
       </c>
       <c r="M4">
-        <v>0.1553264</v>
+        <v>0.2329896</v>
       </c>
       <c r="N4">
-        <v>16.1246736</v>
+        <v>16.0470104</v>
       </c>
       <c r="O4">
-        <v>4.0311684</v>
+        <v>4.0117526</v>
       </c>
       <c r="P4">
-        <v>12.0935052</v>
+        <v>12.0352578</v>
       </c>
       <c r="Q4">
-        <v>15.5135052</v>
+        <v>15.4552578</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1125813602846035</v>
+        <v>0.113100305735709</v>
       </c>
       <c r="T4">
-        <v>1.033086404585177</v>
+        <v>1.041114325669349</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>104.8115452363539</v>
+        <v>69.87436349090261</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1108390465636378</v>
+        <v>0.1105938600483641</v>
       </c>
       <c r="C5">
-        <v>146.4170468273218</v>
+        <v>145.4276789145558</v>
       </c>
       <c r="D5">
-        <v>146.5690468273218</v>
+        <v>147.1236789145558</v>
       </c>
       <c r="E5">
-        <v>-33.368</v>
+        <v>-31.824</v>
       </c>
       <c r="F5">
-        <v>4.632</v>
+        <v>6.176</v>
       </c>
       <c r="G5">
         <v>4.48</v>
@@ -1691,28 +1691,28 @@
         <v>16.28</v>
       </c>
       <c r="M5">
-        <v>0.2329896</v>
+        <v>0.3106528</v>
       </c>
       <c r="N5">
-        <v>16.0470104</v>
+        <v>15.9693472</v>
       </c>
       <c r="O5">
-        <v>4.0117526</v>
+        <v>3.9923368</v>
       </c>
       <c r="P5">
-        <v>12.0352578</v>
+        <v>11.9770104</v>
       </c>
       <c r="Q5">
-        <v>15.4552578</v>
+        <v>15.3970104</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.113100305735709</v>
+        <v>0.1136300625503793</v>
       </c>
       <c r="T5">
-        <v>1.041114325669349</v>
+        <v>1.049309495109441</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>69.87436349090261</v>
+        <v>52.40577261817695</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1105938600483641</v>
+        <v>0.1103486735330905</v>
       </c>
       <c r="C6">
-        <v>145.4276789145558</v>
+        <v>144.4425245138973</v>
       </c>
       <c r="D6">
-        <v>147.1236789145558</v>
+        <v>147.6825245138973</v>
       </c>
       <c r="E6">
-        <v>-31.824</v>
+        <v>-30.28</v>
       </c>
       <c r="F6">
-        <v>6.176</v>
+        <v>7.720000000000001</v>
       </c>
       <c r="G6">
         <v>4.48</v>
@@ -1773,28 +1773,28 @@
         <v>16.28</v>
       </c>
       <c r="M6">
-        <v>0.3106528</v>
+        <v>0.388316</v>
       </c>
       <c r="N6">
-        <v>15.9693472</v>
+        <v>15.891684</v>
       </c>
       <c r="O6">
-        <v>3.9923368</v>
+        <v>3.972921</v>
       </c>
       <c r="P6">
-        <v>11.9770104</v>
+        <v>11.918763</v>
       </c>
       <c r="Q6">
-        <v>15.3970104</v>
+        <v>15.338763</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1136300625503793</v>
+        <v>0.1141709721400953</v>
       </c>
       <c r="T6">
-        <v>1.049309495109441</v>
+        <v>1.057677194432483</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>52.40577261817695</v>
+        <v>41.92461809454156</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1103486735330905</v>
+        <v>0.1101034870178168</v>
       </c>
       <c r="C7">
-        <v>144.4425245138973</v>
+        <v>143.4616318231843</v>
       </c>
       <c r="D7">
-        <v>147.6825245138973</v>
+        <v>148.2456318231844</v>
       </c>
       <c r="E7">
-        <v>-30.28</v>
+        <v>-28.736</v>
       </c>
       <c r="F7">
-        <v>7.720000000000001</v>
+        <v>9.264000000000001</v>
       </c>
       <c r="G7">
         <v>4.48</v>
@@ -1855,28 +1855,28 @@
         <v>16.28</v>
       </c>
       <c r="M7">
-        <v>0.388316</v>
+        <v>0.4659792</v>
       </c>
       <c r="N7">
-        <v>15.891684</v>
+        <v>15.8140208</v>
       </c>
       <c r="O7">
-        <v>3.972921</v>
+        <v>3.9535052</v>
       </c>
       <c r="P7">
-        <v>11.918763</v>
+        <v>11.8605156</v>
       </c>
       <c r="Q7">
-        <v>15.338763</v>
+        <v>15.2805156</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1141709721400953</v>
+        <v>0.114723390444486</v>
       </c>
       <c r="T7">
-        <v>1.057677194432483</v>
+        <v>1.066222929911334</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>41.92461809454156</v>
+        <v>34.9371817454513</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1101034870178168</v>
+        <v>0.1098583005025432</v>
       </c>
       <c r="C8">
-        <v>143.4616318231843</v>
+        <v>142.485049778174</v>
       </c>
       <c r="D8">
-        <v>148.2456318231844</v>
+        <v>148.813049778174</v>
       </c>
       <c r="E8">
-        <v>-28.736</v>
+        <v>-27.192</v>
       </c>
       <c r="F8">
-        <v>9.263999999999999</v>
+        <v>10.808</v>
       </c>
       <c r="G8">
         <v>4.48</v>
@@ -1937,28 +1937,28 @@
         <v>16.28</v>
       </c>
       <c r="M8">
-        <v>0.4659791999999999</v>
+        <v>0.5436424</v>
       </c>
       <c r="N8">
-        <v>15.8140208</v>
+        <v>15.7363576</v>
       </c>
       <c r="O8">
-        <v>3.9535052</v>
+        <v>3.9340894</v>
       </c>
       <c r="P8">
-        <v>11.8605156</v>
+        <v>11.8022682</v>
       </c>
       <c r="Q8">
-        <v>15.2805156</v>
+        <v>15.2222682</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.114723390444486</v>
+        <v>0.115287688712412</v>
       </c>
       <c r="T8">
-        <v>1.066222929911334</v>
+        <v>1.074952444647795</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>34.9371817454513</v>
+        <v>29.9461557818154</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1098583005025432</v>
+        <v>0.1096131139872696</v>
       </c>
       <c r="C9">
-        <v>142.4850497781741</v>
+        <v>141.5128280667187</v>
       </c>
       <c r="D9">
-        <v>148.8130497781741</v>
+        <v>149.3848280667187</v>
       </c>
       <c r="E9">
-        <v>-27.192</v>
+        <v>-25.648</v>
       </c>
       <c r="F9">
-        <v>10.808</v>
+        <v>12.352</v>
       </c>
       <c r="G9">
         <v>4.48</v>
@@ -2019,28 +2019,28 @@
         <v>16.28</v>
       </c>
       <c r="M9">
-        <v>0.5436424000000001</v>
+        <v>0.6213056</v>
       </c>
       <c r="N9">
-        <v>15.7363576</v>
+        <v>15.6586944</v>
       </c>
       <c r="O9">
-        <v>3.9340894</v>
+        <v>3.9146736</v>
       </c>
       <c r="P9">
-        <v>11.8022682</v>
+        <v>11.7440208</v>
       </c>
       <c r="Q9">
-        <v>15.2222682</v>
+        <v>15.1640208</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.115287688712412</v>
+        <v>0.1158642543339886</v>
       </c>
       <c r="T9">
-        <v>1.074952444647795</v>
+        <v>1.083871731443744</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>29.9461557818154</v>
+        <v>26.20288630908848</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1096131139872696</v>
+        <v>0.1093679274719959</v>
       </c>
       <c r="C10">
-        <v>141.5128280667187</v>
+        <v>140.545017143271</v>
       </c>
       <c r="D10">
-        <v>149.3848280667187</v>
+        <v>149.9610171432711</v>
       </c>
       <c r="E10">
-        <v>-25.648</v>
+        <v>-24.104</v>
       </c>
       <c r="F10">
-        <v>12.352</v>
+        <v>13.896</v>
       </c>
       <c r="G10">
         <v>4.48</v>
@@ -2101,28 +2101,28 @@
         <v>16.28</v>
       </c>
       <c r="M10">
-        <v>0.6213056</v>
+        <v>0.6989688000000001</v>
       </c>
       <c r="N10">
-        <v>15.6586944</v>
+        <v>15.5810312</v>
       </c>
       <c r="O10">
-        <v>3.9146736</v>
+        <v>3.8952578</v>
       </c>
       <c r="P10">
-        <v>11.7440208</v>
+        <v>11.6857734</v>
       </c>
       <c r="Q10">
-        <v>15.1640208</v>
+        <v>15.1057734</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1158642543339886</v>
+        <v>0.116453491727468</v>
       </c>
       <c r="T10">
-        <v>1.083871731443744</v>
+        <v>1.092987046520923</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>26.20288630908848</v>
+        <v>23.29145449696753</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1093679274719959</v>
+        <v>0.1091227409567223</v>
       </c>
       <c r="C11">
-        <v>140.545017143271</v>
+        <v>139.5816682437245</v>
       </c>
       <c r="D11">
-        <v>149.9610171432711</v>
+        <v>150.5416682437245</v>
       </c>
       <c r="E11">
-        <v>-24.104</v>
+        <v>-22.56</v>
       </c>
       <c r="F11">
-        <v>13.896</v>
+        <v>15.44</v>
       </c>
       <c r="G11">
         <v>4.48</v>
@@ -2183,28 +2183,28 @@
         <v>16.28</v>
       </c>
       <c r="M11">
-        <v>0.6989688000000001</v>
+        <v>0.776632</v>
       </c>
       <c r="N11">
-        <v>15.5810312</v>
+        <v>15.503368</v>
       </c>
       <c r="O11">
-        <v>3.8952578</v>
+        <v>3.875842</v>
       </c>
       <c r="P11">
-        <v>11.6857734</v>
+        <v>11.627526</v>
       </c>
       <c r="Q11">
-        <v>15.1057734</v>
+        <v>15.047526</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.116453491727468</v>
+        <v>0.1170558232852469</v>
       </c>
       <c r="T11">
-        <v>1.092987046520923</v>
+        <v>1.102304924155373</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>23.29145449696753</v>
+        <v>20.96230904727078</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1091227409567223</v>
+        <v>0.1088775544414486</v>
       </c>
       <c r="C12">
-        <v>139.5816682437245</v>
+        <v>138.6228334006017</v>
       </c>
       <c r="D12">
-        <v>150.5416682437245</v>
+        <v>151.1268334006017</v>
       </c>
       <c r="E12">
-        <v>-22.56</v>
+        <v>-21.016</v>
       </c>
       <c r="F12">
-        <v>15.44</v>
+        <v>16.984</v>
       </c>
       <c r="G12">
         <v>4.48</v>
@@ -2265,28 +2265,28 @@
         <v>16.28</v>
       </c>
       <c r="M12">
-        <v>0.776632</v>
+        <v>0.8542952</v>
       </c>
       <c r="N12">
-        <v>15.503368</v>
+        <v>15.4257048</v>
       </c>
       <c r="O12">
-        <v>3.875842</v>
+        <v>3.8564262</v>
       </c>
       <c r="P12">
-        <v>11.627526</v>
+        <v>11.5692786</v>
       </c>
       <c r="Q12">
-        <v>15.047526</v>
+        <v>14.9892786</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1170558232852469</v>
+        <v>0.1176716903836501</v>
       </c>
       <c r="T12">
-        <v>1.102304924155373</v>
+        <v>1.111832192298462</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.96230904727078</v>
+        <v>19.05664458842798</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1088775544414486</v>
+        <v>0.108632367926175</v>
       </c>
       <c r="C13">
-        <v>138.6228334006017</v>
+        <v>137.6685654585972</v>
       </c>
       <c r="D13">
-        <v>151.1268334006017</v>
+        <v>151.7165654585972</v>
       </c>
       <c r="E13">
-        <v>-21.016</v>
+        <v>-19.472</v>
       </c>
       <c r="F13">
-        <v>16.984</v>
+        <v>18.528</v>
       </c>
       <c r="G13">
         <v>4.48</v>
@@ -2347,28 +2347,28 @@
         <v>16.28</v>
       </c>
       <c r="M13">
-        <v>0.8542952</v>
+        <v>0.9319583999999999</v>
       </c>
       <c r="N13">
-        <v>15.4257048</v>
+        <v>15.3480416</v>
       </c>
       <c r="O13">
-        <v>3.8564262</v>
+        <v>3.8370104</v>
       </c>
       <c r="P13">
-        <v>11.5692786</v>
+        <v>11.5110312</v>
       </c>
       <c r="Q13">
-        <v>14.9892786</v>
+        <v>14.9310312</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1176716903836501</v>
+        <v>0.1183015544615625</v>
       </c>
       <c r="T13">
-        <v>1.111832192298462</v>
+        <v>1.121575989262984</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>19.05664458842798</v>
+        <v>17.46859087272565</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.108632367926175</v>
+        <v>0.1083871814109013</v>
       </c>
       <c r="C14">
-        <v>137.6685654585972</v>
+        <v>136.7189180904862</v>
       </c>
       <c r="D14">
-        <v>151.7165654585972</v>
+        <v>152.3109180904862</v>
       </c>
       <c r="E14">
-        <v>-19.472</v>
+        <v>-17.928</v>
       </c>
       <c r="F14">
-        <v>18.528</v>
+        <v>20.072</v>
       </c>
       <c r="G14">
         <v>4.48</v>
@@ -2429,28 +2429,28 @@
         <v>16.28</v>
       </c>
       <c r="M14">
-        <v>0.9319583999999999</v>
+        <v>1.0096216</v>
       </c>
       <c r="N14">
-        <v>15.3480416</v>
+        <v>15.2703784</v>
       </c>
       <c r="O14">
-        <v>3.8370104</v>
+        <v>3.817594600000001</v>
       </c>
       <c r="P14">
-        <v>11.5110312</v>
+        <v>11.4527838</v>
       </c>
       <c r="Q14">
-        <v>14.9310312</v>
+        <v>14.8727838</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1183015544615625</v>
+        <v>0.1189458981734498</v>
       </c>
       <c r="T14">
-        <v>1.121575989262984</v>
+        <v>1.131543781560024</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.46859087272565</v>
+        <v>16.12485311328522</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1083871814109013</v>
+        <v>0.1081419948956276</v>
       </c>
       <c r="C15">
-        <v>136.7189180904862</v>
+        <v>135.7739458134081</v>
       </c>
       <c r="D15">
-        <v>152.3109180904862</v>
+        <v>152.9099458134081</v>
       </c>
       <c r="E15">
-        <v>-17.928</v>
+        <v>-16.384</v>
       </c>
       <c r="F15">
-        <v>20.072</v>
+        <v>21.616</v>
       </c>
       <c r="G15">
         <v>4.48</v>
@@ -2511,28 +2511,28 @@
         <v>16.28</v>
       </c>
       <c r="M15">
-        <v>1.0096216</v>
+        <v>1.0872848</v>
       </c>
       <c r="N15">
-        <v>15.2703784</v>
+        <v>15.1927152</v>
       </c>
       <c r="O15">
-        <v>3.817594600000001</v>
+        <v>3.7981788</v>
       </c>
       <c r="P15">
-        <v>11.4527838</v>
+        <v>11.3945364</v>
       </c>
       <c r="Q15">
-        <v>14.8727838</v>
+        <v>14.8145364</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1189458981734498</v>
+        <v>0.1196052266228229</v>
       </c>
       <c r="T15">
-        <v>1.131543781560024</v>
+        <v>1.141743382980252</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.12485311328522</v>
+        <v>14.9730778909077</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1081419948956276</v>
+        <v>0.107896808380354</v>
       </c>
       <c r="C16">
-        <v>135.7739458134081</v>
+        <v>134.8337040055366</v>
       </c>
       <c r="D16">
-        <v>152.9099458134081</v>
+        <v>153.5137040055366</v>
       </c>
       <c r="E16">
-        <v>-16.384</v>
+        <v>-14.84</v>
       </c>
       <c r="F16">
-        <v>21.616</v>
+        <v>23.16</v>
       </c>
       <c r="G16">
         <v>4.48</v>
@@ -2593,28 +2593,28 @@
         <v>16.28</v>
       </c>
       <c r="M16">
-        <v>1.0872848</v>
+        <v>1.164948</v>
       </c>
       <c r="N16">
-        <v>15.1927152</v>
+        <v>15.115052</v>
       </c>
       <c r="O16">
-        <v>3.7981788</v>
+        <v>3.778763</v>
       </c>
       <c r="P16">
-        <v>11.3945364</v>
+        <v>11.336289</v>
       </c>
       <c r="Q16">
-        <v>14.8145364</v>
+        <v>14.756289</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1196052266228229</v>
+        <v>0.1202800686827694</v>
       </c>
       <c r="T16">
-        <v>1.141743382980252</v>
+        <v>1.152182975022132</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.9730778909077</v>
+        <v>13.97487269818052</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.107896808380354</v>
+        <v>0.1076516218650804</v>
       </c>
       <c r="C17">
-        <v>134.8337040055366</v>
+        <v>133.8982489231456</v>
       </c>
       <c r="D17">
-        <v>153.5137040055366</v>
+        <v>154.1222489231456</v>
       </c>
       <c r="E17">
-        <v>-14.84</v>
+        <v>-13.296</v>
       </c>
       <c r="F17">
-        <v>23.16</v>
+        <v>24.704</v>
       </c>
       <c r="G17">
         <v>4.48</v>
@@ -2675,28 +2675,28 @@
         <v>16.28</v>
       </c>
       <c r="M17">
-        <v>1.164948</v>
+        <v>1.2426112</v>
       </c>
       <c r="N17">
-        <v>15.115052</v>
+        <v>15.0373888</v>
       </c>
       <c r="O17">
-        <v>3.778763000000001</v>
+        <v>3.7593472</v>
       </c>
       <c r="P17">
-        <v>11.336289</v>
+        <v>11.2780416</v>
       </c>
       <c r="Q17">
-        <v>14.756289</v>
+        <v>14.6980416</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1202800686827694</v>
+        <v>0.1209709784108099</v>
       </c>
       <c r="T17">
-        <v>1.152182975022132</v>
+        <v>1.162871128779294</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>13.97487269818052</v>
+        <v>13.10144315454424</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1076516218650804</v>
+        <v>0.1075976853498067</v>
       </c>
       <c r="C18">
-        <v>133.8982489231456</v>
+        <v>132.4887655637931</v>
       </c>
       <c r="D18">
-        <v>154.1222489231456</v>
+        <v>154.2567655637931</v>
       </c>
       <c r="E18">
-        <v>-13.296</v>
+        <v>-11.752</v>
       </c>
       <c r="F18">
-        <v>24.704</v>
+        <v>26.248</v>
       </c>
       <c r="G18">
         <v>4.48</v>
@@ -2757,45 +2757,45 @@
         <v>16.28</v>
       </c>
       <c r="M18">
-        <v>1.2426112</v>
+        <v>1.3596464</v>
       </c>
       <c r="N18">
-        <v>15.0373888</v>
+        <v>14.9203536</v>
       </c>
       <c r="O18">
-        <v>3.7593472</v>
+        <v>3.730088400000001</v>
       </c>
       <c r="P18">
-        <v>11.2780416</v>
+        <v>11.1902652</v>
       </c>
       <c r="Q18">
-        <v>14.6980416</v>
+        <v>14.6102652</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1209709784108099</v>
+        <v>0.1216785365660322</v>
       </c>
       <c r="T18">
-        <v>1.162871128779294</v>
+        <v>1.173816828410124</v>
       </c>
       <c r="U18">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>13.10144315454424</v>
+        <v>11.97370139765751</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1075976853498067</v>
+        <v>0.1073637488345331</v>
       </c>
       <c r="C19">
-        <v>132.4887655637931</v>
+        <v>131.5309269148565</v>
       </c>
       <c r="D19">
-        <v>154.2567655637931</v>
+        <v>154.8429269148565</v>
       </c>
       <c r="E19">
-        <v>-11.752</v>
+        <v>-10.20799999999999</v>
       </c>
       <c r="F19">
-        <v>26.248</v>
+        <v>27.79200000000001</v>
       </c>
       <c r="G19">
         <v>4.48</v>
@@ -2839,28 +2839,28 @@
         <v>16.28</v>
       </c>
       <c r="M19">
-        <v>1.3596464</v>
+        <v>1.4396256</v>
       </c>
       <c r="N19">
-        <v>14.9203536</v>
+        <v>14.8403744</v>
       </c>
       <c r="O19">
-        <v>3.730088400000001</v>
+        <v>3.7100936</v>
       </c>
       <c r="P19">
-        <v>11.1902652</v>
+        <v>11.1302808</v>
       </c>
       <c r="Q19">
-        <v>14.6102652</v>
+        <v>14.5502808</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1216785365660322</v>
+        <v>0.1224033522372354</v>
       </c>
       <c r="T19">
-        <v>1.173816828410124</v>
+        <v>1.185029496324632</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.97370139765751</v>
+        <v>11.30849576445431</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1073637488345331</v>
+        <v>0.1071298123192594</v>
       </c>
       <c r="C20">
-        <v>131.5309269148565</v>
+        <v>130.5775599751481</v>
       </c>
       <c r="D20">
-        <v>154.8429269148565</v>
+        <v>155.4335599751481</v>
       </c>
       <c r="E20">
-        <v>-10.208</v>
+        <v>-8.663999999999998</v>
       </c>
       <c r="F20">
-        <v>27.792</v>
+        <v>29.336</v>
       </c>
       <c r="G20">
         <v>4.48</v>
@@ -2921,28 +2921,28 @@
         <v>16.28</v>
       </c>
       <c r="M20">
-        <v>1.4396256</v>
+        <v>1.5196048</v>
       </c>
       <c r="N20">
-        <v>14.8403744</v>
+        <v>14.7603952</v>
       </c>
       <c r="O20">
-        <v>3.7100936</v>
+        <v>3.6900988</v>
       </c>
       <c r="P20">
-        <v>11.1302808</v>
+        <v>11.0702964</v>
       </c>
       <c r="Q20">
-        <v>14.5502808</v>
+        <v>14.4902964</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1224033522372354</v>
+        <v>0.1231460645916783</v>
       </c>
       <c r="T20">
-        <v>1.185029496324632</v>
+        <v>1.196519020237029</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.30849576445431</v>
+        <v>10.71331177685146</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1071298123192594</v>
+        <v>0.1068958758039858</v>
       </c>
       <c r="C21">
-        <v>130.5775599751481</v>
+        <v>129.6287161112811</v>
       </c>
       <c r="D21">
-        <v>155.4335599751481</v>
+        <v>156.0287161112811</v>
       </c>
       <c r="E21">
-        <v>-8.663999999999998</v>
+        <v>-7.119999999999997</v>
       </c>
       <c r="F21">
-        <v>29.336</v>
+        <v>30.88</v>
       </c>
       <c r="G21">
         <v>4.48</v>
@@ -3003,28 +3003,28 @@
         <v>16.28</v>
       </c>
       <c r="M21">
-        <v>1.5196048</v>
+        <v>1.599584</v>
       </c>
       <c r="N21">
-        <v>14.7603952</v>
+        <v>14.680416</v>
       </c>
       <c r="O21">
-        <v>3.6900988</v>
+        <v>3.670104</v>
       </c>
       <c r="P21">
-        <v>11.0702964</v>
+        <v>11.010312</v>
       </c>
       <c r="Q21">
-        <v>14.4902964</v>
+        <v>14.430312</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1231460645916783</v>
+        <v>0.1239073447549822</v>
       </c>
       <c r="T21">
-        <v>1.196519020237029</v>
+        <v>1.208295782247236</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.71331177685146</v>
+        <v>10.17764618800888</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1068958758039858</v>
+        <v>0.1069296892887121</v>
       </c>
       <c r="C22">
-        <v>129.6287161112811</v>
+        <v>127.9984098553441</v>
       </c>
       <c r="D22">
-        <v>156.0287161112811</v>
+        <v>155.9424098553442</v>
       </c>
       <c r="E22">
-        <v>-7.119999999999997</v>
+        <v>-5.575999999999993</v>
       </c>
       <c r="F22">
-        <v>30.88</v>
+        <v>32.42400000000001</v>
       </c>
       <c r="G22">
         <v>4.48</v>
@@ -3085,45 +3085,45 @@
         <v>16.28</v>
       </c>
       <c r="M22">
-        <v>1.599584</v>
+        <v>1.734684</v>
       </c>
       <c r="N22">
-        <v>14.680416</v>
+        <v>14.545316</v>
       </c>
       <c r="O22">
-        <v>3.670104</v>
+        <v>3.636329</v>
       </c>
       <c r="P22">
-        <v>11.010312</v>
+        <v>10.908987</v>
       </c>
       <c r="Q22">
-        <v>14.430312</v>
+        <v>14.328987</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1239073447549822</v>
+        <v>0.1246878978338128</v>
       </c>
       <c r="T22">
-        <v>1.208295782247236</v>
+        <v>1.220370690131119</v>
       </c>
       <c r="U22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>10.17764618800888</v>
+        <v>9.384994615734046</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1069296892887121</v>
+        <v>0.1067085027734385</v>
       </c>
       <c r="C23">
-        <v>127.9984098553441</v>
+        <v>127.0207077718695</v>
       </c>
       <c r="D23">
-        <v>155.9424098553442</v>
+        <v>156.5087077718695</v>
       </c>
       <c r="E23">
-        <v>-5.576000000000001</v>
+        <v>-4.031999999999996</v>
       </c>
       <c r="F23">
-        <v>32.424</v>
+        <v>33.968</v>
       </c>
       <c r="G23">
         <v>4.48</v>
@@ -3167,28 +3167,28 @@
         <v>16.28</v>
       </c>
       <c r="M23">
-        <v>1.734684</v>
+        <v>1.817288</v>
       </c>
       <c r="N23">
-        <v>14.545316</v>
+        <v>14.462712</v>
       </c>
       <c r="O23">
-        <v>3.636329</v>
+        <v>3.615678</v>
       </c>
       <c r="P23">
-        <v>10.908987</v>
+        <v>10.847034</v>
       </c>
       <c r="Q23">
-        <v>14.328987</v>
+        <v>14.267034</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1246878978338128</v>
+        <v>0.1254884650941519</v>
       </c>
       <c r="T23">
-        <v>1.220370690131119</v>
+        <v>1.232755211037665</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.384994615734049</v>
+        <v>8.9584039513825</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1067085027734385</v>
+        <v>0.1064873162581648</v>
       </c>
       <c r="C24">
-        <v>127.0207077718695</v>
+        <v>126.0471336502322</v>
       </c>
       <c r="D24">
-        <v>156.5087077718695</v>
+        <v>157.0791336502323</v>
       </c>
       <c r="E24">
-        <v>-4.031999999999996</v>
+        <v>-2.488</v>
       </c>
       <c r="F24">
-        <v>33.968</v>
+        <v>35.512</v>
       </c>
       <c r="G24">
         <v>4.48</v>
@@ -3249,28 +3249,28 @@
         <v>16.28</v>
       </c>
       <c r="M24">
-        <v>1.817288</v>
+        <v>1.899892</v>
       </c>
       <c r="N24">
-        <v>14.462712</v>
+        <v>14.380108</v>
       </c>
       <c r="O24">
-        <v>3.615678</v>
+        <v>3.595027</v>
       </c>
       <c r="P24">
-        <v>10.847034</v>
+        <v>10.785081</v>
       </c>
       <c r="Q24">
-        <v>14.267034</v>
+        <v>14.205081</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1254884650941519</v>
+        <v>0.126309826309305</v>
       </c>
       <c r="T24">
-        <v>1.232755211037665</v>
+        <v>1.245461407811915</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.9584039513825</v>
+        <v>8.568908127409347</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1064873162581648</v>
+        <v>0.1062661297428912</v>
       </c>
       <c r="C25">
-        <v>126.0471336502322</v>
+        <v>125.0777327909749</v>
       </c>
       <c r="D25">
-        <v>157.0791336502323</v>
+        <v>157.6537327909749</v>
       </c>
       <c r="E25">
-        <v>-2.488</v>
+        <v>-0.9439999999999955</v>
       </c>
       <c r="F25">
-        <v>35.512</v>
+        <v>37.056</v>
       </c>
       <c r="G25">
         <v>4.48</v>
@@ -3331,28 +3331,28 @@
         <v>16.28</v>
       </c>
       <c r="M25">
-        <v>1.899892</v>
+        <v>1.982496</v>
       </c>
       <c r="N25">
-        <v>14.380108</v>
+        <v>14.297504</v>
       </c>
       <c r="O25">
-        <v>3.595027</v>
+        <v>3.574376</v>
       </c>
       <c r="P25">
-        <v>10.785081</v>
+        <v>10.723128</v>
       </c>
       <c r="Q25">
-        <v>14.205081</v>
+        <v>14.143128</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.126309826309305</v>
+        <v>0.1271528022932779</v>
       </c>
       <c r="T25">
-        <v>1.245461407811915</v>
+        <v>1.258501978185486</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.568908127409347</v>
+        <v>8.21187028876729</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1062661297428912</v>
+        <v>0.1060449432276176</v>
       </c>
       <c r="C26">
-        <v>125.0777327909749</v>
+        <v>124.1125511599153</v>
       </c>
       <c r="D26">
-        <v>157.6537327909749</v>
+        <v>158.2325511599153</v>
       </c>
       <c r="E26">
-        <v>-0.9440000000000026</v>
+        <v>0.6000000000000014</v>
       </c>
       <c r="F26">
-        <v>37.056</v>
+        <v>38.6</v>
       </c>
       <c r="G26">
         <v>4.48</v>
@@ -3413,28 +3413,28 @@
         <v>16.28</v>
       </c>
       <c r="M26">
-        <v>1.982496</v>
+        <v>2.0651</v>
       </c>
       <c r="N26">
-        <v>14.297504</v>
+        <v>14.2149</v>
       </c>
       <c r="O26">
-        <v>3.574376</v>
+        <v>3.553725</v>
       </c>
       <c r="P26">
-        <v>10.723128</v>
+        <v>10.661175</v>
       </c>
       <c r="Q26">
-        <v>14.143128</v>
+        <v>14.081175</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1271528022932779</v>
+        <v>0.1280182576368234</v>
       </c>
       <c r="T26">
-        <v>1.258501978185486</v>
+        <v>1.271890297102353</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.211870288767294</v>
+        <v>7.883395477216599</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1060449432276176</v>
+        <v>0.1059797567123439</v>
       </c>
       <c r="C27">
-        <v>124.1125511599153</v>
+        <v>122.7399481408349</v>
       </c>
       <c r="D27">
-        <v>158.2325511599153</v>
+        <v>158.403948140835</v>
       </c>
       <c r="E27">
-        <v>0.6000000000000014</v>
+        <v>2.144000000000005</v>
       </c>
       <c r="F27">
-        <v>38.6</v>
+        <v>40.14400000000001</v>
       </c>
       <c r="G27">
         <v>4.48</v>
@@ -3495,45 +3495,45 @@
         <v>16.28</v>
       </c>
       <c r="M27">
-        <v>2.0651</v>
+        <v>2.1798192</v>
       </c>
       <c r="N27">
-        <v>14.2149</v>
+        <v>14.1001808</v>
       </c>
       <c r="O27">
-        <v>3.553725</v>
+        <v>3.5250452</v>
       </c>
       <c r="P27">
-        <v>10.661175</v>
+        <v>10.5751356</v>
       </c>
       <c r="Q27">
-        <v>14.081175</v>
+        <v>13.9951356</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1280182576368234</v>
+        <v>0.1289071036653296</v>
       </c>
       <c r="T27">
-        <v>1.271890297102353</v>
+        <v>1.285640462476433</v>
       </c>
       <c r="U27">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>7.883395477216599</v>
+        <v>7.468509314900978</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1059797567123439</v>
+        <v>0.1057645701970703</v>
       </c>
       <c r="C28">
-        <v>122.7399481408349</v>
+        <v>121.764390364201</v>
       </c>
       <c r="D28">
-        <v>158.403948140835</v>
+        <v>158.972390364201</v>
       </c>
       <c r="E28">
-        <v>2.144000000000005</v>
+        <v>3.688000000000002</v>
       </c>
       <c r="F28">
-        <v>40.14400000000001</v>
+        <v>41.688</v>
       </c>
       <c r="G28">
         <v>4.48</v>
@@ -3577,28 +3577,28 @@
         <v>16.28</v>
       </c>
       <c r="M28">
-        <v>2.1798192</v>
+        <v>2.2636584</v>
       </c>
       <c r="N28">
-        <v>14.1001808</v>
+        <v>14.0163416</v>
       </c>
       <c r="O28">
-        <v>3.5250452</v>
+        <v>3.5040854</v>
       </c>
       <c r="P28">
-        <v>10.5751356</v>
+        <v>10.5122562</v>
       </c>
       <c r="Q28">
-        <v>13.9951356</v>
+        <v>13.9322562</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1289071036653296</v>
+        <v>0.1298203016398223</v>
       </c>
       <c r="T28">
-        <v>1.285640462476433</v>
+        <v>1.299767344710076</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.468509314900978</v>
+        <v>7.191897858793535</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1057645701970703</v>
+        <v>0.1055493836817966</v>
       </c>
       <c r="C29">
-        <v>121.764390364201</v>
+        <v>120.7929270599664</v>
       </c>
       <c r="D29">
-        <v>158.972390364201</v>
+        <v>159.5449270599664</v>
       </c>
       <c r="E29">
-        <v>3.688000000000002</v>
+        <v>5.232000000000006</v>
       </c>
       <c r="F29">
-        <v>41.688</v>
+        <v>43.23200000000001</v>
       </c>
       <c r="G29">
         <v>4.48</v>
@@ -3659,28 +3659,28 @@
         <v>16.28</v>
       </c>
       <c r="M29">
-        <v>2.2636584</v>
+        <v>2.347497600000001</v>
       </c>
       <c r="N29">
-        <v>14.0163416</v>
+        <v>13.9325024</v>
       </c>
       <c r="O29">
-        <v>3.5040854</v>
+        <v>3.4831256</v>
       </c>
       <c r="P29">
-        <v>10.5122562</v>
+        <v>10.4493768</v>
       </c>
       <c r="Q29">
-        <v>13.9322562</v>
+        <v>13.8693768</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1298203016398223</v>
+        <v>0.1307588662247175</v>
       </c>
       <c r="T29">
-        <v>1.299767344710076</v>
+        <v>1.314286640339098</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.191897858793535</v>
+        <v>6.935044363836623</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1055493836817966</v>
+        <v>0.105334197166523</v>
       </c>
       <c r="C30">
-        <v>120.7929270599664</v>
+        <v>119.8256026265755</v>
       </c>
       <c r="D30">
-        <v>159.5449270599664</v>
+        <v>160.1216026265755</v>
       </c>
       <c r="E30">
-        <v>5.232000000000006</v>
+        <v>6.77600000000001</v>
       </c>
       <c r="F30">
-        <v>43.23200000000001</v>
+        <v>44.77600000000001</v>
       </c>
       <c r="G30">
         <v>4.48</v>
@@ -3741,28 +3741,28 @@
         <v>16.28</v>
       </c>
       <c r="M30">
-        <v>2.347497600000001</v>
+        <v>2.4313368</v>
       </c>
       <c r="N30">
-        <v>13.9325024</v>
+        <v>13.8486632</v>
       </c>
       <c r="O30">
-        <v>3.4831256</v>
+        <v>3.4621658</v>
       </c>
       <c r="P30">
-        <v>10.4493768</v>
+        <v>10.3864974</v>
       </c>
       <c r="Q30">
-        <v>13.8693768</v>
+        <v>13.8064974</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1307588662247175</v>
+        <v>0.1317238692486239</v>
       </c>
       <c r="T30">
-        <v>1.314286640339098</v>
+        <v>1.329214930211192</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.935044363836623</v>
+        <v>6.69590490301467</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1053341971665229</v>
+        <v>0.1051190106512493</v>
       </c>
       <c r="C31">
-        <v>119.8256026265756</v>
+        <v>118.8624621067146</v>
       </c>
       <c r="D31">
-        <v>160.1216026265756</v>
+        <v>160.7024621067146</v>
       </c>
       <c r="E31">
-        <v>6.775999999999996</v>
+        <v>8.32</v>
       </c>
       <c r="F31">
-        <v>44.776</v>
+        <v>46.32</v>
       </c>
       <c r="G31">
         <v>4.48</v>
@@ -3823,28 +3823,28 @@
         <v>16.28</v>
       </c>
       <c r="M31">
-        <v>2.4313368</v>
+        <v>2.515176</v>
       </c>
       <c r="N31">
-        <v>13.8486632</v>
+        <v>13.764824</v>
       </c>
       <c r="O31">
-        <v>3.4621658</v>
+        <v>3.441206</v>
       </c>
       <c r="P31">
-        <v>10.3864974</v>
+        <v>10.323618</v>
       </c>
       <c r="Q31">
-        <v>13.8064974</v>
+        <v>13.743618</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1317238692486239</v>
+        <v>0.132716443787499</v>
       </c>
       <c r="T31">
-        <v>1.329214930211192</v>
+        <v>1.344569742651059</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.695904903014672</v>
+        <v>6.472708072914182</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1051190106512493</v>
+        <v>0.1049038241359757</v>
       </c>
       <c r="C32">
-        <v>118.8624621067146</v>
+        <v>117.9035511990392</v>
       </c>
       <c r="D32">
-        <v>160.7024621067146</v>
+        <v>161.2875511990393</v>
       </c>
       <c r="E32">
-        <v>8.32</v>
+        <v>9.864000000000004</v>
       </c>
       <c r="F32">
-        <v>46.32</v>
+        <v>47.864</v>
       </c>
       <c r="G32">
         <v>4.48</v>
@@ -3905,28 +3905,28 @@
         <v>16.28</v>
       </c>
       <c r="M32">
-        <v>2.515176</v>
+        <v>2.5990152</v>
       </c>
       <c r="N32">
-        <v>13.764824</v>
+        <v>13.6809848</v>
       </c>
       <c r="O32">
-        <v>3.441206</v>
+        <v>3.4202462</v>
       </c>
       <c r="P32">
-        <v>10.323618</v>
+        <v>10.2607386</v>
       </c>
       <c r="Q32">
-        <v>13.743618</v>
+        <v>13.6807386</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.132716443787499</v>
+        <v>0.1337377886028633</v>
       </c>
       <c r="T32">
-        <v>1.344569742651059</v>
+        <v>1.360369622118169</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.472708072914182</v>
+        <v>6.263911038304047</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1049038241359757</v>
+        <v>0.104928637620702</v>
       </c>
       <c r="C33">
-        <v>117.9035511990392</v>
+        <v>116.2918664637017</v>
       </c>
       <c r="D33">
-        <v>161.2875511990393</v>
+        <v>161.2198664637017</v>
       </c>
       <c r="E33">
-        <v>9.864000000000004</v>
+        <v>11.408</v>
       </c>
       <c r="F33">
-        <v>47.864</v>
+        <v>49.408</v>
       </c>
       <c r="G33">
         <v>4.48</v>
@@ -3987,45 +3987,45 @@
         <v>16.28</v>
       </c>
       <c r="M33">
-        <v>2.5990152</v>
+        <v>2.7322624</v>
       </c>
       <c r="N33">
-        <v>13.6809848</v>
+        <v>13.5477376</v>
       </c>
       <c r="O33">
-        <v>3.4202462</v>
+        <v>3.3869344</v>
       </c>
       <c r="P33">
-        <v>10.2607386</v>
+        <v>10.1608032</v>
       </c>
       <c r="Q33">
-        <v>13.6807386</v>
+        <v>13.5808032</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1337377886028633</v>
+        <v>0.1347891729716206</v>
       </c>
       <c r="T33">
-        <v>1.360369622118169</v>
+        <v>1.376634203922547</v>
       </c>
       <c r="U33">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>6.263911038304047</v>
+        <v>5.958432103739377</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.104928637620702</v>
+        <v>0.1047209511054284</v>
       </c>
       <c r="C34">
-        <v>116.2918664637017</v>
+        <v>115.3161395759061</v>
       </c>
       <c r="D34">
-        <v>161.2198664637017</v>
+        <v>161.7881395759061</v>
       </c>
       <c r="E34">
-        <v>11.408</v>
+        <v>12.95200000000001</v>
       </c>
       <c r="F34">
-        <v>49.408</v>
+        <v>50.95200000000001</v>
       </c>
       <c r="G34">
         <v>4.48</v>
@@ -4069,28 +4069,28 @@
         <v>16.28</v>
       </c>
       <c r="M34">
-        <v>2.7322624</v>
+        <v>2.817645600000001</v>
       </c>
       <c r="N34">
-        <v>13.5477376</v>
+        <v>13.4623544</v>
       </c>
       <c r="O34">
-        <v>3.3869344</v>
+        <v>3.3655886</v>
       </c>
       <c r="P34">
-        <v>10.1608032</v>
+        <v>10.0967658</v>
       </c>
       <c r="Q34">
-        <v>13.5808032</v>
+        <v>13.5167658</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1347891729716206</v>
+        <v>0.1358719419484006</v>
       </c>
       <c r="T34">
-        <v>1.376634203922547</v>
+        <v>1.393384295631533</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.958432103739377</v>
+        <v>5.777873555141213</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1047209511054284</v>
+        <v>0.1045132645901547</v>
       </c>
       <c r="C35">
-        <v>115.3161395759061</v>
+        <v>114.3444329947048</v>
       </c>
       <c r="D35">
-        <v>161.7881395759061</v>
+        <v>162.3604329947048</v>
       </c>
       <c r="E35">
-        <v>12.95200000000001</v>
+        <v>14.496</v>
       </c>
       <c r="F35">
-        <v>50.95200000000001</v>
+        <v>52.496</v>
       </c>
       <c r="G35">
         <v>4.48</v>
@@ -4151,28 +4151,28 @@
         <v>16.28</v>
       </c>
       <c r="M35">
-        <v>2.817645600000001</v>
+        <v>2.9030288</v>
       </c>
       <c r="N35">
-        <v>13.4623544</v>
+        <v>13.3769712</v>
       </c>
       <c r="O35">
-        <v>3.3655886</v>
+        <v>3.3442428</v>
       </c>
       <c r="P35">
-        <v>10.0967658</v>
+        <v>10.0327284</v>
       </c>
       <c r="Q35">
-        <v>13.5167658</v>
+        <v>13.4527284</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1358719419484006</v>
+        <v>0.1369875221062951</v>
       </c>
       <c r="T35">
-        <v>1.393384295631533</v>
+        <v>1.410641965877156</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.777873555141213</v>
+        <v>5.607936097637061</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1045132645901547</v>
+        <v>0.1043055780748811</v>
       </c>
       <c r="C36">
-        <v>114.3444329947048</v>
+        <v>113.3767895346544</v>
       </c>
       <c r="D36">
-        <v>162.3604329947048</v>
+        <v>162.9367895346545</v>
       </c>
       <c r="E36">
-        <v>14.496</v>
+        <v>16.04000000000001</v>
       </c>
       <c r="F36">
-        <v>52.496</v>
+        <v>54.04000000000001</v>
       </c>
       <c r="G36">
         <v>4.48</v>
@@ -4233,28 +4233,28 @@
         <v>16.28</v>
       </c>
       <c r="M36">
-        <v>2.9030288</v>
+        <v>2.988412</v>
       </c>
       <c r="N36">
-        <v>13.3769712</v>
+        <v>13.291588</v>
       </c>
       <c r="O36">
-        <v>3.3442428</v>
+        <v>3.322897</v>
       </c>
       <c r="P36">
-        <v>10.0327284</v>
+        <v>9.968691</v>
       </c>
       <c r="Q36">
-        <v>13.4527284</v>
+        <v>13.388691</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1369875221062951</v>
+        <v>0.1381374278075093</v>
       </c>
       <c r="T36">
-        <v>1.410641965877156</v>
+        <v>1.428430641361105</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.607936097637061</v>
+        <v>5.447709351990287</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1043055780748811</v>
+        <v>0.1040978915596074</v>
       </c>
       <c r="C37">
-        <v>113.3767895346544</v>
+        <v>112.4132526204202</v>
       </c>
       <c r="D37">
-        <v>162.9367895346545</v>
+        <v>163.5172526204202</v>
       </c>
       <c r="E37">
-        <v>16.04000000000001</v>
+        <v>17.58400000000001</v>
       </c>
       <c r="F37">
-        <v>54.04000000000001</v>
+        <v>55.58400000000001</v>
       </c>
       <c r="G37">
         <v>4.48</v>
@@ -4315,28 +4315,28 @@
         <v>16.28</v>
       </c>
       <c r="M37">
-        <v>2.988412</v>
+        <v>3.073795200000001</v>
       </c>
       <c r="N37">
-        <v>13.291588</v>
+        <v>13.2062048</v>
       </c>
       <c r="O37">
-        <v>3.322897</v>
+        <v>3.3015512</v>
       </c>
       <c r="P37">
-        <v>9.968691</v>
+        <v>9.9046536</v>
       </c>
       <c r="Q37">
-        <v>13.388691</v>
+        <v>13.3246536</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1381374278075093</v>
+        <v>0.1393232680618866</v>
       </c>
       <c r="T37">
-        <v>1.428430641361105</v>
+        <v>1.446775212953927</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.447709351990287</v>
+        <v>5.296384092212779</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1040978915596074</v>
+        <v>0.1038902050443338</v>
       </c>
       <c r="C38">
-        <v>112.4132526204201</v>
+        <v>111.4538662976819</v>
       </c>
       <c r="D38">
-        <v>163.5172526204202</v>
+        <v>164.1018662976819</v>
       </c>
       <c r="E38">
-        <v>17.584</v>
+        <v>19.128</v>
       </c>
       <c r="F38">
-        <v>55.584</v>
+        <v>57.128</v>
       </c>
       <c r="G38">
         <v>4.48</v>
@@ -4397,28 +4397,28 @@
         <v>16.28</v>
       </c>
       <c r="M38">
-        <v>3.0737952</v>
+        <v>3.1591784</v>
       </c>
       <c r="N38">
-        <v>13.2062048</v>
+        <v>13.1208216</v>
       </c>
       <c r="O38">
-        <v>3.3015512</v>
+        <v>3.2802054</v>
       </c>
       <c r="P38">
-        <v>9.904653600000001</v>
+        <v>9.840616200000001</v>
       </c>
       <c r="Q38">
-        <v>13.3246536</v>
+        <v>13.2606162</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1393232680618866</v>
+        <v>0.140546754038625</v>
       </c>
       <c r="T38">
-        <v>1.446775212953927</v>
+        <v>1.465702151898902</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.29638409221278</v>
+        <v>5.15323857620703</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1038902050443338</v>
+        <v>0.1036825185290601</v>
       </c>
       <c r="C39">
-        <v>111.4538662976819</v>
+        <v>110.4986752442752</v>
       </c>
       <c r="D39">
-        <v>164.1018662976819</v>
+        <v>164.6906752442752</v>
       </c>
       <c r="E39">
-        <v>19.128</v>
+        <v>20.672</v>
       </c>
       <c r="F39">
-        <v>57.128</v>
+        <v>58.672</v>
       </c>
       <c r="G39">
         <v>4.48</v>
@@ -4479,28 +4479,28 @@
         <v>16.28</v>
       </c>
       <c r="M39">
-        <v>3.1591784</v>
+        <v>3.2445616</v>
       </c>
       <c r="N39">
-        <v>13.1208216</v>
+        <v>13.0354384</v>
       </c>
       <c r="O39">
-        <v>3.2802054</v>
+        <v>3.2588596</v>
       </c>
       <c r="P39">
-        <v>9.840616200000001</v>
+        <v>9.776578799999999</v>
       </c>
       <c r="Q39">
-        <v>13.2606162</v>
+        <v>13.1965788</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.140546754038625</v>
+        <v>0.1418097073049357</v>
       </c>
       <c r="T39">
-        <v>1.465702151898902</v>
+        <v>1.485239637261458</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.15323857620703</v>
+        <v>5.017627034727896</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1036825185290601</v>
+        <v>0.1034748320137865</v>
       </c>
       <c r="C40">
-        <v>110.4986752442752</v>
+        <v>109.5477247815738</v>
       </c>
       <c r="D40">
-        <v>164.6906752442752</v>
+        <v>165.2837247815738</v>
       </c>
       <c r="E40">
-        <v>20.672</v>
+        <v>22.216</v>
       </c>
       <c r="F40">
-        <v>58.672</v>
+        <v>60.216</v>
       </c>
       <c r="G40">
         <v>4.48</v>
@@ -4561,28 +4561,28 @@
         <v>16.28</v>
       </c>
       <c r="M40">
-        <v>3.2445616</v>
+        <v>3.3299448</v>
       </c>
       <c r="N40">
-        <v>13.0354384</v>
+        <v>12.9500552</v>
       </c>
       <c r="O40">
-        <v>3.2588596</v>
+        <v>3.2375138</v>
       </c>
       <c r="P40">
-        <v>9.776578799999999</v>
+        <v>9.712541400000001</v>
       </c>
       <c r="Q40">
-        <v>13.1965788</v>
+        <v>13.1325414</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1418097073049357</v>
+        <v>0.1431140688750598</v>
       </c>
       <c r="T40">
-        <v>1.485239637261458</v>
+        <v>1.505417695914589</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.017627034727896</v>
+        <v>4.888969931273335</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1034748320137865</v>
+        <v>0.1032671454985128</v>
       </c>
       <c r="C41">
-        <v>109.5477247815738</v>
+        <v>108.6010608861176</v>
       </c>
       <c r="D41">
-        <v>165.2837247815738</v>
+        <v>165.8810608861176</v>
       </c>
       <c r="E41">
-        <v>22.216</v>
+        <v>23.76000000000001</v>
       </c>
       <c r="F41">
-        <v>60.216</v>
+        <v>61.76000000000001</v>
       </c>
       <c r="G41">
         <v>4.48</v>
@@ -4643,28 +4643,28 @@
         <v>16.28</v>
       </c>
       <c r="M41">
-        <v>3.3299448</v>
+        <v>3.415328000000001</v>
       </c>
       <c r="N41">
-        <v>12.9500552</v>
+        <v>12.864672</v>
       </c>
       <c r="O41">
-        <v>3.2375138</v>
+        <v>3.216168</v>
       </c>
       <c r="P41">
-        <v>9.712541400000001</v>
+        <v>9.648504000000001</v>
       </c>
       <c r="Q41">
-        <v>13.1325414</v>
+        <v>13.068504</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1431140688750598</v>
+        <v>0.1444619091641881</v>
       </c>
       <c r="T41">
-        <v>1.505417695914589</v>
+        <v>1.526268356522824</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.888969931273335</v>
+        <v>4.766745682991502</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1032671454985128</v>
+        <v>0.1030594589832392</v>
       </c>
       <c r="C42">
-        <v>108.6010608861176</v>
+        <v>107.6587302014951</v>
       </c>
       <c r="D42">
-        <v>165.8810608861176</v>
+        <v>166.4827302014951</v>
       </c>
       <c r="E42">
-        <v>23.76000000000001</v>
+        <v>25.30400000000001</v>
       </c>
       <c r="F42">
-        <v>61.76000000000001</v>
+        <v>63.30400000000001</v>
       </c>
       <c r="G42">
         <v>4.48</v>
@@ -4725,28 +4725,28 @@
         <v>16.28</v>
       </c>
       <c r="M42">
-        <v>3.415328000000001</v>
+        <v>3.5007112</v>
       </c>
       <c r="N42">
-        <v>12.864672</v>
+        <v>12.7792888</v>
       </c>
       <c r="O42">
-        <v>3.216168</v>
+        <v>3.1948222</v>
       </c>
       <c r="P42">
-        <v>9.648504000000001</v>
+        <v>9.584466599999999</v>
       </c>
       <c r="Q42">
-        <v>13.068504</v>
+        <v>13.0044666</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1444619091641881</v>
+        <v>0.1458554389546427</v>
       </c>
       <c r="T42">
-        <v>1.526268356522824</v>
+        <v>1.547825819185576</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.766745682991502</v>
+        <v>4.65048359316244</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1030594589832392</v>
+        <v>0.1028517724679656</v>
       </c>
       <c r="C43">
-        <v>107.6587302014951</v>
+        <v>106.7207800504845</v>
       </c>
       <c r="D43">
-        <v>166.4827302014951</v>
+        <v>167.0887800504846</v>
       </c>
       <c r="E43">
-        <v>25.30400000000001</v>
+        <v>26.84800000000001</v>
       </c>
       <c r="F43">
-        <v>63.30400000000001</v>
+        <v>64.84800000000001</v>
       </c>
       <c r="G43">
         <v>4.48</v>
@@ -4807,28 +4807,28 @@
         <v>16.28</v>
       </c>
       <c r="M43">
-        <v>3.5007112</v>
+        <v>3.586094400000001</v>
       </c>
       <c r="N43">
-        <v>12.7792888</v>
+        <v>12.6939056</v>
       </c>
       <c r="O43">
-        <v>3.1948222</v>
+        <v>3.1734764</v>
       </c>
       <c r="P43">
-        <v>9.584466599999999</v>
+        <v>9.520429200000001</v>
       </c>
       <c r="Q43">
-        <v>13.0044666</v>
+        <v>12.9404292</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1458554389546427</v>
+        <v>0.1472970214964923</v>
       </c>
       <c r="T43">
-        <v>1.547825819185576</v>
+        <v>1.570126642629802</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.65048359316244</v>
+        <v>4.539757793325239</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1028517724679656</v>
+        <v>0.1034503359526919</v>
       </c>
       <c r="C44">
-        <v>106.7207800504845</v>
+        <v>103.4419550786446</v>
       </c>
       <c r="D44">
-        <v>167.0887800504846</v>
+        <v>165.3539550786446</v>
       </c>
       <c r="E44">
-        <v>26.848</v>
+        <v>28.392</v>
       </c>
       <c r="F44">
-        <v>64.848</v>
+        <v>66.392</v>
       </c>
       <c r="G44">
         <v>4.48</v>
@@ -4889,45 +4889,45 @@
         <v>16.28</v>
       </c>
       <c r="M44">
-        <v>3.5860944</v>
+        <v>3.8374576</v>
       </c>
       <c r="N44">
-        <v>12.6939056</v>
+        <v>12.4425424</v>
       </c>
       <c r="O44">
-        <v>3.1734764</v>
+        <v>3.1106356</v>
       </c>
       <c r="P44">
-        <v>9.520429200000001</v>
+        <v>9.331906800000001</v>
       </c>
       <c r="Q44">
-        <v>12.9404292</v>
+        <v>12.7519068</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1472970214964923</v>
+        <v>0.1487891858819156</v>
       </c>
       <c r="T44">
-        <v>1.570126642629802</v>
+        <v>1.593209951107158</v>
       </c>
       <c r="U44">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V44">
         <v>0.25</v>
       </c>
       <c r="W44">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>4.53975779332524</v>
+        <v>4.242392150469623</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1034503359526919</v>
+        <v>0.1032613994374183</v>
       </c>
       <c r="C45">
-        <v>103.4419550786446</v>
+        <v>102.4416487645824</v>
       </c>
       <c r="D45">
-        <v>165.3539550786446</v>
+        <v>165.8976487645824</v>
       </c>
       <c r="E45">
-        <v>28.392</v>
+        <v>29.93600000000001</v>
       </c>
       <c r="F45">
-        <v>66.392</v>
+        <v>67.93600000000001</v>
       </c>
       <c r="G45">
         <v>4.48</v>
@@ -4971,28 +4971,28 @@
         <v>16.28</v>
       </c>
       <c r="M45">
-        <v>3.8374576</v>
+        <v>3.926700800000001</v>
       </c>
       <c r="N45">
-        <v>12.4425424</v>
+        <v>12.3532992</v>
       </c>
       <c r="O45">
-        <v>3.1106356</v>
+        <v>3.0883248</v>
       </c>
       <c r="P45">
-        <v>9.331906800000001</v>
+        <v>9.2649744</v>
       </c>
       <c r="Q45">
-        <v>12.7519068</v>
+        <v>12.6849744</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1487891858819156</v>
+        <v>0.1503346418525326</v>
       </c>
       <c r="T45">
-        <v>1.593209951107158</v>
+        <v>1.617117663458706</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.242392150469623</v>
+        <v>4.145974147049859</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1032613994374183</v>
+        <v>0.1030724629221446</v>
       </c>
       <c r="C46">
-        <v>102.4416487645824</v>
+        <v>101.4449296400754</v>
       </c>
       <c r="D46">
-        <v>165.8976487645824</v>
+        <v>166.4449296400754</v>
       </c>
       <c r="E46">
-        <v>29.93600000000001</v>
+        <v>31.48</v>
       </c>
       <c r="F46">
-        <v>67.93600000000001</v>
+        <v>69.48</v>
       </c>
       <c r="G46">
         <v>4.48</v>
@@ -5053,28 +5053,28 @@
         <v>16.28</v>
       </c>
       <c r="M46">
-        <v>3.926700800000001</v>
+        <v>4.015944</v>
       </c>
       <c r="N46">
-        <v>12.3532992</v>
+        <v>12.264056</v>
       </c>
       <c r="O46">
-        <v>3.0883248</v>
+        <v>3.066014</v>
       </c>
       <c r="P46">
-        <v>9.2649744</v>
+        <v>9.198042000000001</v>
       </c>
       <c r="Q46">
-        <v>12.6849744</v>
+        <v>12.618042</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1503346418525326</v>
+        <v>0.1519362962220811</v>
       </c>
       <c r="T46">
-        <v>1.617117663458706</v>
+        <v>1.641894747168492</v>
       </c>
       <c r="U46">
         <v>0.0578</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.145974147049859</v>
+        <v>4.053841388226529</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1030724629221446</v>
+        <v>0.104091026406871</v>
       </c>
       <c r="C47">
-        <v>101.4449296400754</v>
+        <v>96.99251066035328</v>
       </c>
       <c r="D47">
-        <v>166.4449296400754</v>
+        <v>163.5365106603533</v>
       </c>
       <c r="E47">
-        <v>31.48</v>
+        <v>33.024</v>
       </c>
       <c r="F47">
-        <v>69.48</v>
+        <v>71.024</v>
       </c>
       <c r="G47">
         <v>4.48</v>
@@ -5135,45 +5135,45 @@
         <v>16.28</v>
       </c>
       <c r="M47">
-        <v>4.015944</v>
+        <v>4.3537712</v>
       </c>
       <c r="N47">
-        <v>12.264056</v>
+        <v>11.9262288</v>
       </c>
       <c r="O47">
-        <v>3.066014</v>
+        <v>2.9815572</v>
       </c>
       <c r="P47">
-        <v>9.198042000000001</v>
+        <v>8.9446716</v>
       </c>
       <c r="Q47">
-        <v>12.618042</v>
+        <v>12.3646716</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1519362962220811</v>
+        <v>0.1535972711238351</v>
       </c>
       <c r="T47">
-        <v>1.641894747168492</v>
+        <v>1.667589500645307</v>
       </c>
       <c r="U47">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.053841388226529</v>
+        <v>3.73928698871452</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.104091026406871</v>
+        <v>0.1039283398915973</v>
       </c>
       <c r="C48">
-        <v>96.99251066035328</v>
+        <v>95.90620797441665</v>
       </c>
       <c r="D48">
-        <v>163.5365106603533</v>
+        <v>163.9942079744167</v>
       </c>
       <c r="E48">
-        <v>33.024</v>
+        <v>34.56800000000001</v>
       </c>
       <c r="F48">
-        <v>71.024</v>
+        <v>72.56800000000001</v>
       </c>
       <c r="G48">
         <v>4.48</v>
@@ -5217,28 +5217,28 @@
         <v>16.28</v>
       </c>
       <c r="M48">
-        <v>4.3537712</v>
+        <v>4.4484184</v>
       </c>
       <c r="N48">
-        <v>11.9262288</v>
+        <v>11.8315816</v>
       </c>
       <c r="O48">
-        <v>2.9815572</v>
+        <v>2.9578954</v>
       </c>
       <c r="P48">
-        <v>8.9446716</v>
+        <v>8.8736862</v>
       </c>
       <c r="Q48">
-        <v>12.3646716</v>
+        <v>12.2936862</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1535972711238351</v>
+        <v>0.1553209243237685</v>
       </c>
       <c r="T48">
-        <v>1.667589500645307</v>
+        <v>1.69425386746087</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.73928698871452</v>
+        <v>3.659727691082296</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1039283398915973</v>
+        <v>0.1037656533763237</v>
       </c>
       <c r="C49">
-        <v>95.90620797441665</v>
+        <v>94.82247443681992</v>
       </c>
       <c r="D49">
-        <v>163.9942079744167</v>
+        <v>164.4544744368199</v>
       </c>
       <c r="E49">
-        <v>34.56800000000001</v>
+        <v>36.11200000000001</v>
       </c>
       <c r="F49">
-        <v>72.56800000000001</v>
+        <v>74.11200000000001</v>
       </c>
       <c r="G49">
         <v>4.48</v>
@@ -5299,28 +5299,28 @@
         <v>16.28</v>
       </c>
       <c r="M49">
-        <v>4.4484184</v>
+        <v>4.5430656</v>
       </c>
       <c r="N49">
-        <v>11.8315816</v>
+        <v>11.7369344</v>
       </c>
       <c r="O49">
-        <v>2.9578954</v>
+        <v>2.9342336</v>
       </c>
       <c r="P49">
-        <v>8.8736862</v>
+        <v>8.8027008</v>
       </c>
       <c r="Q49">
-        <v>12.2936862</v>
+        <v>12.2227008</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1553209243237685</v>
+        <v>0.1571108718775455</v>
       </c>
       <c r="T49">
-        <v>1.69425386746087</v>
+        <v>1.721943786846263</v>
       </c>
       <c r="U49">
         <v>0.0613</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.659727691082296</v>
+        <v>3.583483364184748</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1037656533763237</v>
+        <v>0.10360296686105</v>
       </c>
       <c r="C50">
-        <v>94.82247443681993</v>
+        <v>93.74133174017601</v>
       </c>
       <c r="D50">
-        <v>164.4544744368199</v>
+        <v>164.917331740176</v>
       </c>
       <c r="E50">
-        <v>36.11199999999999</v>
+        <v>37.65600000000001</v>
       </c>
       <c r="F50">
-        <v>74.11199999999999</v>
+        <v>75.65600000000001</v>
       </c>
       <c r="G50">
         <v>4.48</v>
@@ -5381,28 +5381,28 @@
         <v>16.28</v>
       </c>
       <c r="M50">
-        <v>4.543065599999999</v>
+        <v>4.6377128</v>
       </c>
       <c r="N50">
-        <v>11.7369344</v>
+        <v>11.6422872</v>
       </c>
       <c r="O50">
-        <v>2.934233600000001</v>
+        <v>2.9105718</v>
       </c>
       <c r="P50">
-        <v>8.802700800000002</v>
+        <v>8.731715400000002</v>
       </c>
       <c r="Q50">
-        <v>12.2227008</v>
+        <v>12.1517154</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1571108718775455</v>
+        <v>0.1589710134530393</v>
       </c>
       <c r="T50">
-        <v>1.721943786846263</v>
+        <v>1.750719585423239</v>
       </c>
       <c r="U50">
         <v>0.0613</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.583483364184749</v>
+        <v>3.510351050629958</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.10360296686105</v>
+        <v>0.1044902803457764</v>
       </c>
       <c r="C51">
-        <v>93.74133174017601</v>
+        <v>89.70401646793646</v>
       </c>
       <c r="D51">
-        <v>164.917331740176</v>
+        <v>162.4240164679365</v>
       </c>
       <c r="E51">
-        <v>37.65600000000001</v>
+        <v>39.2</v>
       </c>
       <c r="F51">
-        <v>75.65600000000001</v>
+        <v>77.2</v>
       </c>
       <c r="G51">
         <v>4.48</v>
@@ -5463,45 +5463,45 @@
         <v>16.28</v>
       </c>
       <c r="M51">
-        <v>4.6377128</v>
+        <v>4.94852</v>
       </c>
       <c r="N51">
-        <v>11.6422872</v>
+        <v>11.33148</v>
       </c>
       <c r="O51">
-        <v>2.9105718</v>
+        <v>2.83287</v>
       </c>
       <c r="P51">
-        <v>8.731715400000002</v>
+        <v>8.498610000000001</v>
       </c>
       <c r="Q51">
-        <v>12.1517154</v>
+        <v>11.91861</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1589710134530393</v>
+        <v>0.1609055606915527</v>
       </c>
       <c r="T51">
-        <v>1.750719585423239</v>
+        <v>1.780646415943294</v>
       </c>
       <c r="U51">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>3.510351050629958</v>
+        <v>3.289872527543589</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1044902803457764</v>
+        <v>0.1043485938305027</v>
       </c>
       <c r="C52">
-        <v>89.70401646793646</v>
+        <v>88.55307958669744</v>
       </c>
       <c r="D52">
-        <v>162.4240164679365</v>
+        <v>162.8170795866974</v>
       </c>
       <c r="E52">
-        <v>39.2</v>
+        <v>40.744</v>
       </c>
       <c r="F52">
-        <v>77.2</v>
+        <v>78.744</v>
       </c>
       <c r="G52">
         <v>4.48</v>
@@ -5545,28 +5545,28 @@
         <v>16.28</v>
       </c>
       <c r="M52">
-        <v>4.94852</v>
+        <v>5.0474904</v>
       </c>
       <c r="N52">
-        <v>11.33148</v>
+        <v>11.2325096</v>
       </c>
       <c r="O52">
-        <v>2.83287</v>
+        <v>2.8081274</v>
       </c>
       <c r="P52">
-        <v>8.498610000000001</v>
+        <v>8.4243822</v>
       </c>
       <c r="Q52">
-        <v>11.91861</v>
+        <v>11.8443822</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1609055606915527</v>
+        <v>0.1629190690418423</v>
       </c>
       <c r="T52">
-        <v>1.780646415943294</v>
+        <v>1.811794749749883</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.289872527543589</v>
+        <v>3.22536522308195</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1043485938305027</v>
+        <v>0.1042069073152291</v>
       </c>
       <c r="C53">
-        <v>88.55307958669744</v>
+        <v>87.4040497313957</v>
       </c>
       <c r="D53">
-        <v>162.8170795866974</v>
+        <v>163.2120497313957</v>
       </c>
       <c r="E53">
-        <v>40.744</v>
+        <v>42.28800000000001</v>
       </c>
       <c r="F53">
-        <v>78.744</v>
+        <v>80.28800000000001</v>
       </c>
       <c r="G53">
         <v>4.48</v>
@@ -5627,28 +5627,28 @@
         <v>16.28</v>
       </c>
       <c r="M53">
-        <v>5.0474904</v>
+        <v>5.146460800000001</v>
       </c>
       <c r="N53">
-        <v>11.2325096</v>
+        <v>11.1335392</v>
       </c>
       <c r="O53">
-        <v>2.8081274</v>
+        <v>2.7833848</v>
       </c>
       <c r="P53">
-        <v>8.4243822</v>
+        <v>8.350154400000001</v>
       </c>
       <c r="Q53">
-        <v>11.8443822</v>
+        <v>11.7701544</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1629190690418423</v>
+        <v>0.1650164735733939</v>
       </c>
       <c r="T53">
-        <v>1.811794749749883</v>
+        <v>1.844240930798412</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.22536522308195</v>
+        <v>3.163338968791912</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1042069073152291</v>
+        <v>0.1040652207999554</v>
       </c>
       <c r="C54">
-        <v>87.4040497313957</v>
+        <v>86.25694081426833</v>
       </c>
       <c r="D54">
-        <v>163.2120497313957</v>
+        <v>163.6089408142684</v>
       </c>
       <c r="E54">
-        <v>42.28800000000001</v>
+        <v>43.83200000000001</v>
       </c>
       <c r="F54">
-        <v>80.28800000000001</v>
+        <v>81.83200000000001</v>
       </c>
       <c r="G54">
         <v>4.48</v>
@@ -5709,28 +5709,28 @@
         <v>16.28</v>
       </c>
       <c r="M54">
-        <v>5.146460800000001</v>
+        <v>5.245431200000001</v>
       </c>
       <c r="N54">
-        <v>11.1335392</v>
+        <v>11.0345688</v>
       </c>
       <c r="O54">
-        <v>2.7833848</v>
+        <v>2.7586422</v>
       </c>
       <c r="P54">
-        <v>8.350154400000001</v>
+        <v>8.2759266</v>
       </c>
       <c r="Q54">
-        <v>11.7701544</v>
+        <v>11.6959266</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1650164735733939</v>
+        <v>0.1672031293616073</v>
       </c>
       <c r="T54">
-        <v>1.844240930798412</v>
+        <v>1.878067800402198</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.163338968791912</v>
+        <v>3.10365332787131</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1040652207999554</v>
+        <v>0.1039235342846818</v>
       </c>
       <c r="C55">
-        <v>86.25694081426833</v>
+        <v>85.11176688320714</v>
       </c>
       <c r="D55">
-        <v>163.6089408142684</v>
+        <v>164.0077668832072</v>
       </c>
       <c r="E55">
-        <v>43.83200000000001</v>
+        <v>45.376</v>
       </c>
       <c r="F55">
-        <v>81.83200000000001</v>
+        <v>83.376</v>
       </c>
       <c r="G55">
         <v>4.48</v>
@@ -5791,28 +5791,28 @@
         <v>16.28</v>
       </c>
       <c r="M55">
-        <v>5.245431200000001</v>
+        <v>5.3444016</v>
       </c>
       <c r="N55">
-        <v>11.0345688</v>
+        <v>10.9355984</v>
       </c>
       <c r="O55">
-        <v>2.7586422</v>
+        <v>2.7338996</v>
       </c>
       <c r="P55">
-        <v>8.2759266</v>
+        <v>8.201698799999999</v>
       </c>
       <c r="Q55">
-        <v>11.6959266</v>
+        <v>11.6216988</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1672031293616073</v>
+        <v>0.1694848571406126</v>
       </c>
       <c r="T55">
-        <v>1.878067800402198</v>
+        <v>1.913365403467018</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.10365332787131</v>
+        <v>3.046178266244064</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1039235342846818</v>
+        <v>0.1069993477694082</v>
       </c>
       <c r="C56">
-        <v>85.11176688320714</v>
+        <v>75.32491268025117</v>
       </c>
       <c r="D56">
-        <v>164.0077668832072</v>
+        <v>155.7649126802512</v>
       </c>
       <c r="E56">
-        <v>45.376</v>
+        <v>46.92000000000002</v>
       </c>
       <c r="F56">
-        <v>83.376</v>
+        <v>84.92000000000002</v>
       </c>
       <c r="G56">
         <v>4.48</v>
@@ -5873,45 +5873,45 @@
         <v>16.28</v>
       </c>
       <c r="M56">
-        <v>5.3444016</v>
+        <v>6.105748000000002</v>
       </c>
       <c r="N56">
-        <v>10.9355984</v>
+        <v>10.174252</v>
       </c>
       <c r="O56">
-        <v>2.7338996</v>
+        <v>2.543563</v>
       </c>
       <c r="P56">
-        <v>8.201698799999999</v>
+        <v>7.630688999999999</v>
       </c>
       <c r="Q56">
-        <v>11.6216988</v>
+        <v>11.050689</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1694848571406126</v>
+        <v>0.1718679950431292</v>
       </c>
       <c r="T56">
-        <v>1.913365403467018</v>
+        <v>1.950231788890275</v>
       </c>
       <c r="U56">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V56">
         <v>0.25</v>
       </c>
       <c r="W56">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>3.046178266244064</v>
+        <v>2.666339979966418</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1069993477694082</v>
+        <v>0.1069161612541345</v>
       </c>
       <c r="C57">
-        <v>75.32491268025117</v>
+        <v>73.99292763704626</v>
       </c>
       <c r="D57">
-        <v>155.7649126802512</v>
+        <v>155.9769276370463</v>
       </c>
       <c r="E57">
-        <v>46.92000000000002</v>
+        <v>48.46400000000001</v>
       </c>
       <c r="F57">
-        <v>84.92000000000002</v>
+        <v>86.46400000000001</v>
       </c>
       <c r="G57">
         <v>4.48</v>
@@ -5955,28 +5955,28 @@
         <v>16.28</v>
       </c>
       <c r="M57">
-        <v>6.105748000000002</v>
+        <v>6.216761600000002</v>
       </c>
       <c r="N57">
-        <v>10.174252</v>
+        <v>10.0632384</v>
       </c>
       <c r="O57">
-        <v>2.543563</v>
+        <v>2.5158096</v>
       </c>
       <c r="P57">
-        <v>7.630688999999999</v>
+        <v>7.5474288</v>
       </c>
       <c r="Q57">
-        <v>11.050689</v>
+        <v>10.9674288</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1718679950431292</v>
+        <v>0.1743594573957602</v>
       </c>
       <c r="T57">
-        <v>1.950231788890275</v>
+        <v>1.988773919105498</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.666339979966418</v>
+        <v>2.618726766038447</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1069161612541345</v>
+        <v>0.1068329747388608</v>
       </c>
       <c r="C58">
-        <v>73.99292763704626</v>
+        <v>72.66152053668344</v>
       </c>
       <c r="D58">
-        <v>155.9769276370463</v>
+        <v>156.1895205366835</v>
       </c>
       <c r="E58">
-        <v>48.46400000000001</v>
+        <v>50.00800000000001</v>
       </c>
       <c r="F58">
-        <v>86.46400000000001</v>
+        <v>88.00800000000001</v>
       </c>
       <c r="G58">
         <v>4.48</v>
@@ -6037,28 +6037,28 @@
         <v>16.28</v>
       </c>
       <c r="M58">
-        <v>6.216761600000002</v>
+        <v>6.327775200000001</v>
       </c>
       <c r="N58">
-        <v>10.0632384</v>
+        <v>9.9522248</v>
       </c>
       <c r="O58">
-        <v>2.5158096</v>
+        <v>2.4880562</v>
       </c>
       <c r="P58">
-        <v>7.5474288</v>
+        <v>7.4641686</v>
       </c>
       <c r="Q58">
-        <v>10.9674288</v>
+        <v>10.8841686</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1743594573957602</v>
+        <v>0.1769668017182811</v>
       </c>
       <c r="T58">
-        <v>1.988773919105498</v>
+        <v>2.029108706540034</v>
       </c>
       <c r="U58">
         <v>0.07190000000000001</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.618726766038447</v>
+        <v>2.572784191195667</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1068329747388608</v>
+        <v>0.1067497882235872</v>
       </c>
       <c r="C59">
-        <v>72.66152053668344</v>
+        <v>71.33069374555566</v>
       </c>
       <c r="D59">
-        <v>156.1895205366835</v>
+        <v>156.4026937455557</v>
       </c>
       <c r="E59">
-        <v>50.00800000000001</v>
+        <v>51.55200000000002</v>
       </c>
       <c r="F59">
-        <v>88.00800000000001</v>
+        <v>89.55200000000002</v>
       </c>
       <c r="G59">
         <v>4.48</v>
@@ -6119,28 +6119,28 @@
         <v>16.28</v>
       </c>
       <c r="M59">
-        <v>6.327775200000001</v>
+        <v>6.438788800000002</v>
       </c>
       <c r="N59">
-        <v>9.9522248</v>
+        <v>9.8412112</v>
       </c>
       <c r="O59">
-        <v>2.4880562</v>
+        <v>2.4603028</v>
       </c>
       <c r="P59">
-        <v>7.4641686</v>
+        <v>7.3809084</v>
       </c>
       <c r="Q59">
-        <v>10.8841686</v>
+        <v>10.8009084</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1769668017182811</v>
+        <v>0.1796983052942553</v>
       </c>
       <c r="T59">
-        <v>2.029108706540034</v>
+        <v>2.071364198138118</v>
       </c>
       <c r="U59">
         <v>0.07190000000000001</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.572784191195667</v>
+        <v>2.528425843071603</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1067497882235872</v>
+        <v>0.1083923517083136</v>
       </c>
       <c r="C60">
-        <v>71.33069374555572</v>
+        <v>65.68233679701871</v>
       </c>
       <c r="D60">
-        <v>156.4026937455557</v>
+        <v>152.2983367970187</v>
       </c>
       <c r="E60">
-        <v>51.55199999999999</v>
+        <v>53.096</v>
       </c>
       <c r="F60">
-        <v>89.55199999999999</v>
+        <v>91.096</v>
       </c>
       <c r="G60">
         <v>4.48</v>
@@ -6201,45 +6201,45 @@
         <v>16.28</v>
       </c>
       <c r="M60">
-        <v>6.4387888</v>
+        <v>6.905076800000001</v>
       </c>
       <c r="N60">
-        <v>9.8412112</v>
+        <v>9.374923200000001</v>
       </c>
       <c r="O60">
-        <v>2.4603028</v>
+        <v>2.3437308</v>
       </c>
       <c r="P60">
-        <v>7.3809084</v>
+        <v>7.031192400000001</v>
       </c>
       <c r="Q60">
-        <v>10.8009084</v>
+        <v>10.4511924</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1796983052942552</v>
+        <v>0.1825630529471062</v>
       </c>
       <c r="T60">
-        <v>2.071364198138118</v>
+        <v>2.115680933228792</v>
       </c>
       <c r="U60">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V60">
         <v>0.25</v>
       </c>
       <c r="W60">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.528425843071604</v>
+        <v>2.357685579977908</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1083923517083136</v>
+        <v>0.1083384151930399</v>
       </c>
       <c r="C61">
-        <v>65.68233679701871</v>
+        <v>64.2696871285461</v>
       </c>
       <c r="D61">
-        <v>152.2983367970187</v>
+        <v>152.4296871285461</v>
       </c>
       <c r="E61">
-        <v>53.096</v>
+        <v>54.64</v>
       </c>
       <c r="F61">
-        <v>91.096</v>
+        <v>92.64</v>
       </c>
       <c r="G61">
         <v>4.48</v>
@@ -6283,28 +6283,28 @@
         <v>16.28</v>
       </c>
       <c r="M61">
-        <v>6.905076800000001</v>
+        <v>7.022112000000001</v>
       </c>
       <c r="N61">
-        <v>9.374923200000001</v>
+        <v>9.257888000000001</v>
       </c>
       <c r="O61">
-        <v>2.3437308</v>
+        <v>2.314472</v>
       </c>
       <c r="P61">
-        <v>7.031192400000001</v>
+        <v>6.943416000000001</v>
       </c>
       <c r="Q61">
-        <v>10.4511924</v>
+        <v>10.363416</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1825630529471062</v>
+        <v>0.1855710379825998</v>
       </c>
       <c r="T61">
-        <v>2.115680933228792</v>
+        <v>2.162213505074</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.357685579977908</v>
+        <v>2.31839082031161</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1083384151930399</v>
+        <v>0.1082844786777663</v>
       </c>
       <c r="C62">
-        <v>64.2696871285461</v>
+        <v>62.85726422292126</v>
       </c>
       <c r="D62">
-        <v>152.4296871285461</v>
+        <v>152.5612642229213</v>
       </c>
       <c r="E62">
-        <v>54.64</v>
+        <v>56.184</v>
       </c>
       <c r="F62">
-        <v>92.64</v>
+        <v>94.184</v>
       </c>
       <c r="G62">
         <v>4.48</v>
@@ -6365,28 +6365,28 @@
         <v>16.28</v>
       </c>
       <c r="M62">
-        <v>7.022112000000001</v>
+        <v>7.1391472</v>
       </c>
       <c r="N62">
-        <v>9.257888000000001</v>
+        <v>9.140852800000001</v>
       </c>
       <c r="O62">
-        <v>2.314472</v>
+        <v>2.2852132</v>
       </c>
       <c r="P62">
-        <v>6.943416000000001</v>
+        <v>6.855639600000001</v>
       </c>
       <c r="Q62">
-        <v>10.363416</v>
+        <v>10.2756396</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1855710379825998</v>
+        <v>0.1887332786609391</v>
       </c>
       <c r="T62">
-        <v>2.162213505074</v>
+        <v>2.21113236265486</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.31839082031161</v>
+        <v>2.280384413421256</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1082844786777663</v>
+        <v>0.1082305421624926</v>
       </c>
       <c r="C63">
-        <v>62.85726422292126</v>
+        <v>61.44506866787557</v>
       </c>
       <c r="D63">
-        <v>152.5612642229213</v>
+        <v>152.6930686678756</v>
       </c>
       <c r="E63">
-        <v>56.184</v>
+        <v>57.72800000000001</v>
       </c>
       <c r="F63">
-        <v>94.184</v>
+        <v>95.72800000000001</v>
       </c>
       <c r="G63">
         <v>4.48</v>
@@ -6447,28 +6447,28 @@
         <v>16.28</v>
       </c>
       <c r="M63">
-        <v>7.1391472</v>
+        <v>7.256182400000001</v>
       </c>
       <c r="N63">
-        <v>9.140852800000001</v>
+        <v>9.023817600000001</v>
       </c>
       <c r="O63">
-        <v>2.2852132</v>
+        <v>2.2559544</v>
       </c>
       <c r="P63">
-        <v>6.855639600000001</v>
+        <v>6.767863200000001</v>
       </c>
       <c r="Q63">
-        <v>10.2756396</v>
+        <v>10.1878632</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1887332786609391</v>
+        <v>0.1920619530591911</v>
       </c>
       <c r="T63">
-        <v>2.21113236265486</v>
+        <v>2.262625896950502</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.280384413421256</v>
+        <v>2.243604019656397</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1082305421624926</v>
+        <v>0.108176605647219</v>
       </c>
       <c r="C64">
-        <v>61.44506866787557</v>
+        <v>60.03310105317344</v>
       </c>
       <c r="D64">
-        <v>152.6930686678756</v>
+        <v>152.8251010531735</v>
       </c>
       <c r="E64">
-        <v>57.72800000000001</v>
+        <v>59.27200000000001</v>
       </c>
       <c r="F64">
-        <v>95.72800000000001</v>
+        <v>97.27200000000001</v>
       </c>
       <c r="G64">
         <v>4.48</v>
@@ -6529,28 +6529,28 @@
         <v>16.28</v>
       </c>
       <c r="M64">
-        <v>7.256182400000001</v>
+        <v>7.373217600000001</v>
       </c>
       <c r="N64">
-        <v>9.023817600000001</v>
+        <v>8.906782400000001</v>
       </c>
       <c r="O64">
-        <v>2.2559544</v>
+        <v>2.2266956</v>
       </c>
       <c r="P64">
-        <v>6.767863200000001</v>
+        <v>6.680086800000001</v>
       </c>
       <c r="Q64">
-        <v>10.1878632</v>
+        <v>10.1000868</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1920619530591911</v>
+        <v>0.1955705558032945</v>
       </c>
       <c r="T64">
-        <v>2.262625896950502</v>
+        <v>2.316902865532395</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.243604019656397</v>
+        <v>2.207991257439629</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.108176605647219</v>
+        <v>0.1081226691319453</v>
       </c>
       <c r="C65">
-        <v>60.03310105317344</v>
+        <v>58.62136197062065</v>
       </c>
       <c r="D65">
-        <v>152.8251010531735</v>
+        <v>152.9573619706207</v>
       </c>
       <c r="E65">
-        <v>59.27200000000001</v>
+        <v>60.816</v>
       </c>
       <c r="F65">
-        <v>97.27200000000001</v>
+        <v>98.816</v>
       </c>
       <c r="G65">
         <v>4.48</v>
@@ -6611,28 +6611,28 @@
         <v>16.28</v>
       </c>
       <c r="M65">
-        <v>7.373217600000001</v>
+        <v>7.4902528</v>
       </c>
       <c r="N65">
-        <v>8.906782400000001</v>
+        <v>8.789747200000001</v>
       </c>
       <c r="O65">
-        <v>2.2266956</v>
+        <v>2.1974368</v>
       </c>
       <c r="P65">
-        <v>6.680086800000001</v>
+        <v>6.592310400000001</v>
       </c>
       <c r="Q65">
-        <v>10.1000868</v>
+        <v>10.0123104</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1955705558032945</v>
+        <v>0.1992740809220704</v>
       </c>
       <c r="T65">
-        <v>2.316902865532395</v>
+        <v>2.374195221257726</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.207991257439629</v>
+        <v>2.173491394042134</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1081226691319453</v>
+        <v>0.1080687326166717</v>
       </c>
       <c r="C66">
-        <v>58.62136197062065</v>
+        <v>57.20985201407359</v>
       </c>
       <c r="D66">
-        <v>152.9573619706207</v>
+        <v>153.0898520140736</v>
       </c>
       <c r="E66">
-        <v>60.816</v>
+        <v>62.36000000000001</v>
       </c>
       <c r="F66">
-        <v>98.816</v>
+        <v>100.36</v>
       </c>
       <c r="G66">
         <v>4.48</v>
@@ -6693,28 +6693,28 @@
         <v>16.28</v>
       </c>
       <c r="M66">
-        <v>7.4902528</v>
+        <v>7.607288000000001</v>
       </c>
       <c r="N66">
-        <v>8.789747200000001</v>
+        <v>8.672712000000001</v>
       </c>
       <c r="O66">
-        <v>2.1974368</v>
+        <v>2.168178</v>
       </c>
       <c r="P66">
-        <v>6.592310400000001</v>
+        <v>6.504534</v>
       </c>
       <c r="Q66">
-        <v>10.0123104</v>
+        <v>9.924534000000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1992740809220704</v>
+        <v>0.2031892360476334</v>
       </c>
       <c r="T66">
-        <v>2.374195221257726</v>
+        <v>2.434761425881648</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.173491394042134</v>
+        <v>2.140053064903024</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1080687326166717</v>
+        <v>0.108014796101398</v>
       </c>
       <c r="C67">
-        <v>57.20985201407359</v>
+        <v>55.7985717794481</v>
       </c>
       <c r="D67">
-        <v>153.0898520140736</v>
+        <v>153.2225717794481</v>
       </c>
       <c r="E67">
-        <v>62.36000000000001</v>
+        <v>63.90400000000001</v>
       </c>
       <c r="F67">
-        <v>100.36</v>
+        <v>101.904</v>
       </c>
       <c r="G67">
         <v>4.48</v>
@@ -6775,28 +6775,28 @@
         <v>16.28</v>
       </c>
       <c r="M67">
-        <v>7.607288000000001</v>
+        <v>7.724323200000001</v>
       </c>
       <c r="N67">
-        <v>8.672712000000001</v>
+        <v>8.555676800000001</v>
       </c>
       <c r="O67">
-        <v>2.168178</v>
+        <v>2.1389192</v>
       </c>
       <c r="P67">
-        <v>6.504534</v>
+        <v>6.4167576</v>
       </c>
       <c r="Q67">
-        <v>9.924534000000001</v>
+        <v>9.8367576</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2031892360476334</v>
+        <v>0.2073346944158766</v>
       </c>
       <c r="T67">
-        <v>2.434761425881648</v>
+        <v>2.498890348424624</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.140053064903024</v>
+        <v>2.1076280184651</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.108014796101398</v>
+        <v>0.1079608595861244</v>
       </c>
       <c r="C68">
-        <v>55.7985717794481</v>
+        <v>54.38752186472803</v>
       </c>
       <c r="D68">
-        <v>153.2225717794481</v>
+        <v>153.355521864728</v>
       </c>
       <c r="E68">
-        <v>63.90400000000001</v>
+        <v>65.44800000000001</v>
       </c>
       <c r="F68">
-        <v>101.904</v>
+        <v>103.448</v>
       </c>
       <c r="G68">
         <v>4.48</v>
@@ -6857,28 +6857,28 @@
         <v>16.28</v>
       </c>
       <c r="M68">
-        <v>7.724323200000001</v>
+        <v>7.841358400000002</v>
       </c>
       <c r="N68">
-        <v>8.555676800000001</v>
+        <v>8.4386416</v>
       </c>
       <c r="O68">
-        <v>2.1389192</v>
+        <v>2.1096604</v>
       </c>
       <c r="P68">
-        <v>6.4167576</v>
+        <v>6.3289812</v>
       </c>
       <c r="Q68">
-        <v>9.8367576</v>
+        <v>9.748981199999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2073346944158766</v>
+        <v>0.2117313926852254</v>
       </c>
       <c r="T68">
-        <v>2.498890348424624</v>
+        <v>2.56690587233384</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.1076280184651</v>
+        <v>2.076170883861143</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1079608595861244</v>
+        <v>0.1079069230708507</v>
       </c>
       <c r="C69">
-        <v>54.38752186472803</v>
+        <v>52.97670286997474</v>
       </c>
       <c r="D69">
-        <v>153.355521864728</v>
+        <v>153.4887028699748</v>
       </c>
       <c r="E69">
-        <v>65.44800000000001</v>
+        <v>66.992</v>
       </c>
       <c r="F69">
-        <v>103.448</v>
+        <v>104.992</v>
       </c>
       <c r="G69">
         <v>4.48</v>
@@ -6939,28 +6939,28 @@
         <v>16.28</v>
       </c>
       <c r="M69">
-        <v>7.841358400000002</v>
+        <v>7.958393600000001</v>
       </c>
       <c r="N69">
-        <v>8.4386416</v>
+        <v>8.3216064</v>
       </c>
       <c r="O69">
-        <v>2.1096604</v>
+        <v>2.0804016</v>
       </c>
       <c r="P69">
-        <v>6.3289812</v>
+        <v>6.2412048</v>
       </c>
       <c r="Q69">
-        <v>9.748981199999999</v>
+        <v>9.6612048</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2117313926852254</v>
+        <v>0.2164028845964086</v>
       </c>
       <c r="T69">
-        <v>2.56690587233384</v>
+        <v>2.639172366487383</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.076170883861143</v>
+        <v>2.045638959098479</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1079069230708507</v>
+        <v>0.1078529865555771</v>
       </c>
       <c r="C70">
-        <v>52.97670286997474</v>
+        <v>51.56611539733571</v>
       </c>
       <c r="D70">
-        <v>153.4887028699748</v>
+        <v>153.6221153973357</v>
       </c>
       <c r="E70">
-        <v>66.992</v>
+        <v>68.53600000000002</v>
       </c>
       <c r="F70">
-        <v>104.992</v>
+        <v>106.536</v>
       </c>
       <c r="G70">
         <v>4.48</v>
@@ -7021,28 +7021,28 @@
         <v>16.28</v>
       </c>
       <c r="M70">
-        <v>7.958393600000001</v>
+        <v>8.075428800000001</v>
       </c>
       <c r="N70">
-        <v>8.3216064</v>
+        <v>8.2045712</v>
       </c>
       <c r="O70">
-        <v>2.0804016</v>
+        <v>2.0511428</v>
       </c>
       <c r="P70">
-        <v>6.2412048</v>
+        <v>6.1534284</v>
       </c>
       <c r="Q70">
-        <v>9.6612048</v>
+        <v>9.573428400000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2164028845964086</v>
+        <v>0.2213757630825068</v>
       </c>
       <c r="T70">
-        <v>2.639172366487383</v>
+        <v>2.716101215102445</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.045638959098479</v>
+        <v>2.01599201766227</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1078529865555771</v>
+        <v>0.1152540500403035</v>
       </c>
       <c r="C71">
-        <v>51.56611539733571</v>
+        <v>33.65205450018328</v>
       </c>
       <c r="D71">
-        <v>153.6221153973357</v>
+        <v>137.2520545001833</v>
       </c>
       <c r="E71">
-        <v>68.53600000000002</v>
+        <v>70.08000000000001</v>
       </c>
       <c r="F71">
-        <v>106.536</v>
+        <v>108.08</v>
       </c>
       <c r="G71">
         <v>4.48</v>
@@ -7103,45 +7103,45 @@
         <v>16.28</v>
       </c>
       <c r="M71">
-        <v>8.075428800000001</v>
+        <v>9.727200000000002</v>
       </c>
       <c r="N71">
-        <v>8.2045712</v>
+        <v>6.5528</v>
       </c>
       <c r="O71">
-        <v>2.0511428</v>
+        <v>1.6382</v>
       </c>
       <c r="P71">
-        <v>6.1534284</v>
+        <v>4.9146</v>
       </c>
       <c r="Q71">
-        <v>9.573428400000001</v>
+        <v>8.3346</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2213757630825068</v>
+        <v>0.2266801668010115</v>
       </c>
       <c r="T71">
-        <v>2.716101215102445</v>
+        <v>2.798158653625177</v>
       </c>
       <c r="U71">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V71">
         <v>0.25</v>
       </c>
       <c r="W71">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.01599201766227</v>
+        <v>1.673657373139238</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1152540500403035</v>
+        <v>0.1153066135250298</v>
       </c>
       <c r="C72">
-        <v>33.65205450018328</v>
+        <v>32.00425939487603</v>
       </c>
       <c r="D72">
-        <v>137.2520545001833</v>
+        <v>137.148259394876</v>
       </c>
       <c r="E72">
-        <v>70.08000000000001</v>
+        <v>71.62400000000001</v>
       </c>
       <c r="F72">
-        <v>108.08</v>
+        <v>109.624</v>
       </c>
       <c r="G72">
         <v>4.48</v>
@@ -7185,28 +7185,28 @@
         <v>16.28</v>
       </c>
       <c r="M72">
-        <v>9.727200000000002</v>
+        <v>9.866160000000001</v>
       </c>
       <c r="N72">
-        <v>6.5528</v>
+        <v>6.41384</v>
       </c>
       <c r="O72">
-        <v>1.6382</v>
+        <v>1.60346</v>
       </c>
       <c r="P72">
-        <v>4.9146</v>
+        <v>4.81038</v>
       </c>
       <c r="Q72">
-        <v>8.3346</v>
+        <v>8.23038</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2266801668010115</v>
+        <v>0.2323503914656201</v>
       </c>
       <c r="T72">
-        <v>2.798158653625177</v>
+        <v>2.885875225839134</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.673657373139238</v>
+        <v>1.650084734080939</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1153066135250298</v>
+        <v>0.1153591770097561</v>
       </c>
       <c r="C73">
-        <v>32.00425939487604</v>
+        <v>30.35662115837223</v>
       </c>
       <c r="D73">
-        <v>137.148259394876</v>
+        <v>137.0446211583723</v>
       </c>
       <c r="E73">
-        <v>71.624</v>
+        <v>73.16800000000001</v>
       </c>
       <c r="F73">
-        <v>109.624</v>
+        <v>111.168</v>
       </c>
       <c r="G73">
         <v>4.48</v>
@@ -7267,28 +7267,28 @@
         <v>16.28</v>
       </c>
       <c r="M73">
-        <v>9.866159999999999</v>
+        <v>10.00512</v>
       </c>
       <c r="N73">
-        <v>6.413840000000002</v>
+        <v>6.274880000000001</v>
       </c>
       <c r="O73">
-        <v>1.603460000000001</v>
+        <v>1.56872</v>
       </c>
       <c r="P73">
-        <v>4.810380000000002</v>
+        <v>4.706160000000001</v>
       </c>
       <c r="Q73">
-        <v>8.230380000000002</v>
+        <v>8.12616</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.23235039146562</v>
+        <v>0.2384256321777005</v>
       </c>
       <c r="T73">
-        <v>2.885875225839133</v>
+        <v>2.979857267496941</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.65008473408094</v>
+        <v>1.627166890552038</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1153591770097561</v>
+        <v>0.1154117404944825</v>
       </c>
       <c r="C74">
-        <v>30.35662115837223</v>
+        <v>28.70913943531924</v>
       </c>
       <c r="D74">
-        <v>137.0446211583723</v>
+        <v>136.9411394353193</v>
       </c>
       <c r="E74">
-        <v>73.16800000000001</v>
+        <v>74.712</v>
       </c>
       <c r="F74">
-        <v>111.168</v>
+        <v>112.712</v>
       </c>
       <c r="G74">
         <v>4.48</v>
@@ -7349,28 +7349,28 @@
         <v>16.28</v>
       </c>
       <c r="M74">
-        <v>10.00512</v>
+        <v>10.14408</v>
       </c>
       <c r="N74">
-        <v>6.274880000000001</v>
+        <v>6.13592</v>
       </c>
       <c r="O74">
-        <v>1.56872</v>
+        <v>1.53398</v>
       </c>
       <c r="P74">
-        <v>4.706160000000001</v>
+        <v>4.601940000000001</v>
       </c>
       <c r="Q74">
-        <v>8.12616</v>
+        <v>8.021940000000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2384256321777005</v>
+        <v>0.2449508907203056</v>
       </c>
       <c r="T74">
-        <v>2.979857267496941</v>
+        <v>3.080800941870145</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.627166890552038</v>
+        <v>1.604876933147215</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1154117404944825</v>
+        <v>0.1154643039792088</v>
       </c>
       <c r="C75">
-        <v>28.70913943531924</v>
+        <v>27.06181387143701</v>
       </c>
       <c r="D75">
-        <v>136.9411394353193</v>
+        <v>136.837813871437</v>
       </c>
       <c r="E75">
-        <v>74.712</v>
+        <v>76.256</v>
       </c>
       <c r="F75">
-        <v>112.712</v>
+        <v>114.256</v>
       </c>
       <c r="G75">
         <v>4.48</v>
@@ -7431,28 +7431,28 @@
         <v>16.28</v>
       </c>
       <c r="M75">
-        <v>10.14408</v>
+        <v>10.28304</v>
       </c>
       <c r="N75">
-        <v>6.13592</v>
+        <v>5.996960000000001</v>
       </c>
       <c r="O75">
-        <v>1.53398</v>
+        <v>1.49924</v>
       </c>
       <c r="P75">
-        <v>4.601940000000001</v>
+        <v>4.497720000000001</v>
       </c>
       <c r="Q75">
-        <v>8.021940000000001</v>
+        <v>7.917720000000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2449508907203056</v>
+        <v>0.2519780922277263</v>
       </c>
       <c r="T75">
-        <v>3.080800941870145</v>
+        <v>3.189509514272054</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.604876933147215</v>
+        <v>1.583189407023604</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1154643039792088</v>
+        <v>0.1155168674639352</v>
       </c>
       <c r="C76">
-        <v>27.06181387143701</v>
+        <v>25.41464411351376</v>
       </c>
       <c r="D76">
-        <v>136.837813871437</v>
+        <v>136.7346441135138</v>
       </c>
       <c r="E76">
-        <v>76.256</v>
+        <v>77.80000000000001</v>
       </c>
       <c r="F76">
-        <v>114.256</v>
+        <v>115.8</v>
       </c>
       <c r="G76">
         <v>4.48</v>
@@ -7513,28 +7513,28 @@
         <v>16.28</v>
       </c>
       <c r="M76">
-        <v>10.28304</v>
+        <v>10.422</v>
       </c>
       <c r="N76">
-        <v>5.996960000000001</v>
+        <v>5.858000000000001</v>
       </c>
       <c r="O76">
-        <v>1.49924</v>
+        <v>1.4645</v>
       </c>
       <c r="P76">
-        <v>4.497720000000001</v>
+        <v>4.3935</v>
       </c>
       <c r="Q76">
-        <v>7.917720000000001</v>
+        <v>7.8135</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2519780922277263</v>
+        <v>0.2595674698557408</v>
       </c>
       <c r="T76">
-        <v>3.189509514272054</v>
+        <v>3.306914772466119</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.583189407023604</v>
+        <v>1.562080214929956</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1155168674639352</v>
+        <v>0.1155694309486616</v>
       </c>
       <c r="C77">
-        <v>25.41464411351376</v>
+        <v>23.76762980940235</v>
       </c>
       <c r="D77">
-        <v>136.7346441135138</v>
+        <v>136.6316298094024</v>
       </c>
       <c r="E77">
-        <v>77.80000000000001</v>
+        <v>79.34400000000001</v>
       </c>
       <c r="F77">
-        <v>115.8</v>
+        <v>117.344</v>
       </c>
       <c r="G77">
         <v>4.48</v>
@@ -7595,28 +7595,28 @@
         <v>16.28</v>
       </c>
       <c r="M77">
-        <v>10.422</v>
+        <v>10.56096</v>
       </c>
       <c r="N77">
-        <v>5.858000000000001</v>
+        <v>5.719040000000001</v>
       </c>
       <c r="O77">
-        <v>1.4645</v>
+        <v>1.42976</v>
       </c>
       <c r="P77">
-        <v>4.3935</v>
+        <v>4.289280000000002</v>
       </c>
       <c r="Q77">
-        <v>7.8135</v>
+        <v>7.709280000000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2595674698557408</v>
+        <v>0.2677892956194232</v>
       </c>
       <c r="T77">
-        <v>3.306914772466119</v>
+        <v>3.434103802176354</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.562080214929956</v>
+        <v>1.541526527891404</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1155694309486616</v>
+        <v>0.1156219944333879</v>
       </c>
       <c r="C78">
-        <v>23.76762980940235</v>
+        <v>22.12077060801599</v>
       </c>
       <c r="D78">
-        <v>136.6316298094024</v>
+        <v>136.528770608016</v>
       </c>
       <c r="E78">
-        <v>79.34400000000001</v>
+        <v>80.88800000000001</v>
       </c>
       <c r="F78">
-        <v>117.344</v>
+        <v>118.888</v>
       </c>
       <c r="G78">
         <v>4.48</v>
@@ -7677,28 +7677,28 @@
         <v>16.28</v>
       </c>
       <c r="M78">
-        <v>10.56096</v>
+        <v>10.69992</v>
       </c>
       <c r="N78">
-        <v>5.719040000000001</v>
+        <v>5.580080000000001</v>
       </c>
       <c r="O78">
-        <v>1.42976</v>
+        <v>1.39502</v>
       </c>
       <c r="P78">
-        <v>4.289280000000002</v>
+        <v>4.18506</v>
       </c>
       <c r="Q78">
-        <v>7.709280000000001</v>
+        <v>7.60506</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2677892956194232</v>
+        <v>0.2767260627538605</v>
       </c>
       <c r="T78">
-        <v>3.434103802176354</v>
+        <v>3.572352747513566</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.541526527891404</v>
+        <v>1.521506702853853</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1156219944333879</v>
+        <v>0.1156745579181143</v>
       </c>
       <c r="C79">
-        <v>22.12077060801599</v>
+        <v>20.47406615932421</v>
       </c>
       <c r="D79">
-        <v>136.528770608016</v>
+        <v>136.4260661593242</v>
       </c>
       <c r="E79">
-        <v>80.88800000000001</v>
+        <v>82.432</v>
       </c>
       <c r="F79">
-        <v>118.888</v>
+        <v>120.432</v>
       </c>
       <c r="G79">
         <v>4.48</v>
@@ -7759,28 +7759,28 @@
         <v>16.28</v>
       </c>
       <c r="M79">
-        <v>10.69992</v>
+        <v>10.83888</v>
       </c>
       <c r="N79">
-        <v>5.580080000000001</v>
+        <v>5.441120000000002</v>
       </c>
       <c r="O79">
-        <v>1.39502</v>
+        <v>1.36028</v>
       </c>
       <c r="P79">
-        <v>4.18506</v>
+        <v>4.080840000000001</v>
       </c>
       <c r="Q79">
-        <v>7.60506</v>
+        <v>7.500840000000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2767260627538605</v>
+        <v>0.2864752632641557</v>
       </c>
       <c r="T79">
-        <v>3.572352747513566</v>
+        <v>3.723169778790525</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.521506702853853</v>
+        <v>1.502000206663419</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1156745579181143</v>
+        <v>0.1531937025297453</v>
       </c>
       <c r="C80">
-        <v>20.47406615932421</v>
+        <v>-28.73184682491168</v>
       </c>
       <c r="D80">
-        <v>136.4260661593242</v>
+        <v>88.76415317508832</v>
       </c>
       <c r="E80">
-        <v>82.432</v>
+        <v>83.97600000000001</v>
       </c>
       <c r="F80">
-        <v>120.432</v>
+        <v>121.976</v>
       </c>
       <c r="G80">
         <v>4.48</v>
@@ -7841,45 +7841,45 @@
         <v>16.28</v>
       </c>
       <c r="M80">
-        <v>10.83888</v>
+        <v>17.9060768</v>
       </c>
       <c r="N80">
-        <v>5.441120000000002</v>
+        <v>-1.626076800000003</v>
       </c>
       <c r="O80">
-        <v>1.36028</v>
+        <v>-0.4065192000000009</v>
       </c>
       <c r="P80">
-        <v>4.080840000000001</v>
+        <v>-1.219557600000003</v>
       </c>
       <c r="Q80">
-        <v>7.500840000000001</v>
+        <v>2.200442399999997</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2864752632641557</v>
+        <v>0.3027705055080398</v>
       </c>
       <c r="T80">
-        <v>3.723169778790525</v>
+        <v>3.975251993795358</v>
       </c>
       <c r="U80">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.25</v>
+        <v>0.2272971374723468</v>
       </c>
       <c r="W80">
-        <v>0.0675</v>
+        <v>0.1134327802190595</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y80">
-        <v>1.502000206663419</v>
+        <v>0.9091885498893871</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1531937025297453</v>
+        <v>0.1542037025297454</v>
       </c>
       <c r="C81">
-        <v>-28.73184682491168</v>
+        <v>-31.10286465377447</v>
       </c>
       <c r="D81">
-        <v>88.76415317508832</v>
+        <v>87.93713534622553</v>
       </c>
       <c r="E81">
-        <v>83.97600000000001</v>
+        <v>85.52000000000001</v>
       </c>
       <c r="F81">
-        <v>121.976</v>
+        <v>123.52</v>
       </c>
       <c r="G81">
         <v>4.48</v>
@@ -7923,37 +7923,37 @@
         <v>16.28</v>
       </c>
       <c r="M81">
-        <v>17.9060768</v>
+        <v>18.132736</v>
       </c>
       <c r="N81">
-        <v>-1.626076800000003</v>
+        <v>-1.852736000000004</v>
       </c>
       <c r="O81">
-        <v>-0.4065192000000009</v>
+        <v>-0.4631840000000009</v>
       </c>
       <c r="P81">
-        <v>-1.219557600000003</v>
+        <v>-1.389552000000003</v>
       </c>
       <c r="Q81">
-        <v>2.200442399999997</v>
+        <v>2.030447999999997</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3027705055080398</v>
+        <v>0.3156190307834418</v>
       </c>
       <c r="T81">
-        <v>3.975251993795358</v>
+        <v>4.174014593485126</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.2272971374723468</v>
+        <v>0.2244559232539425</v>
       </c>
       <c r="W81">
-        <v>0.1134327802190595</v>
+        <v>0.1138498704663213</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.9091885498893871</v>
+        <v>0.8978236930157697</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1542037025297454</v>
+        <v>0.1552137025297453</v>
       </c>
       <c r="C82">
-        <v>-31.10286465377447</v>
+        <v>-33.45861404755394</v>
       </c>
       <c r="D82">
-        <v>87.93713534622553</v>
+        <v>87.12538595244607</v>
       </c>
       <c r="E82">
-        <v>85.52000000000001</v>
+        <v>87.06400000000001</v>
       </c>
       <c r="F82">
-        <v>123.52</v>
+        <v>125.064</v>
       </c>
       <c r="G82">
         <v>4.48</v>
@@ -8005,37 +8005,37 @@
         <v>16.28</v>
       </c>
       <c r="M82">
-        <v>18.132736</v>
+        <v>18.3593952</v>
       </c>
       <c r="N82">
-        <v>-1.852736000000004</v>
+        <v>-2.0793952</v>
       </c>
       <c r="O82">
-        <v>-0.4631840000000009</v>
+        <v>-0.5198488000000001</v>
       </c>
       <c r="P82">
-        <v>-1.389552000000003</v>
+        <v>-1.5595464</v>
       </c>
       <c r="Q82">
-        <v>2.030447999999997</v>
+        <v>1.8604536</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3156190307834418</v>
+        <v>0.3298200324036229</v>
       </c>
       <c r="T82">
-        <v>4.174014593485126</v>
+        <v>4.393699572089606</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.2244559232539425</v>
+        <v>0.2216848624730296</v>
       </c>
       <c r="W82">
-        <v>0.1138498704663213</v>
+        <v>0.1142566621889593</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8978236930157697</v>
+        <v>0.8867394498921184</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1552137025297453</v>
+        <v>0.1562237025297454</v>
       </c>
       <c r="C83">
-        <v>-33.45861404755394</v>
+        <v>-35.79951396845875</v>
       </c>
       <c r="D83">
-        <v>87.12538595244607</v>
+        <v>86.32848603154126</v>
       </c>
       <c r="E83">
-        <v>87.06400000000001</v>
+        <v>88.60800000000002</v>
       </c>
       <c r="F83">
-        <v>125.064</v>
+        <v>126.608</v>
       </c>
       <c r="G83">
         <v>4.48</v>
@@ -8087,37 +8087,37 @@
         <v>16.28</v>
       </c>
       <c r="M83">
-        <v>18.3593952</v>
+        <v>18.58605440000001</v>
       </c>
       <c r="N83">
-        <v>-2.0793952</v>
+        <v>-2.306054400000004</v>
       </c>
       <c r="O83">
-        <v>-0.5198488000000001</v>
+        <v>-0.5765136000000011</v>
       </c>
       <c r="P83">
-        <v>-1.5595464</v>
+        <v>-1.729540800000003</v>
       </c>
       <c r="Q83">
-        <v>1.8604536</v>
+        <v>1.690459199999997</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3298200324036229</v>
+        <v>0.3455989230927132</v>
       </c>
       <c r="T83">
-        <v>4.393699572089606</v>
+        <v>4.637793992761252</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.2216848624730296</v>
+        <v>0.2189813885404316</v>
       </c>
       <c r="W83">
-        <v>0.1142566621889593</v>
+        <v>0.1146535321622646</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8867394498921184</v>
+        <v>0.8759255541617266</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1562237025297454</v>
+        <v>0.1572337025297454</v>
       </c>
       <c r="C84">
-        <v>-35.79951396845875</v>
+        <v>-38.12596818933132</v>
       </c>
       <c r="D84">
-        <v>86.32848603154126</v>
+        <v>85.54603181066869</v>
       </c>
       <c r="E84">
-        <v>88.60800000000002</v>
+        <v>90.15200000000002</v>
       </c>
       <c r="F84">
-        <v>126.608</v>
+        <v>128.152</v>
       </c>
       <c r="G84">
         <v>4.48</v>
@@ -8169,37 +8169,37 @@
         <v>16.28</v>
       </c>
       <c r="M84">
-        <v>18.58605440000001</v>
+        <v>18.81271360000001</v>
       </c>
       <c r="N84">
-        <v>-2.306054400000004</v>
+        <v>-2.532713600000005</v>
       </c>
       <c r="O84">
-        <v>-0.5765136000000011</v>
+        <v>-0.6331784000000011</v>
       </c>
       <c r="P84">
-        <v>-1.729540800000003</v>
+        <v>-1.899535200000003</v>
       </c>
       <c r="Q84">
-        <v>1.690459199999997</v>
+        <v>1.520464799999997</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3455989230927132</v>
+        <v>0.3632341538628727</v>
       </c>
       <c r="T84">
-        <v>4.637793992761252</v>
+        <v>4.910605404100149</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.2189813885404316</v>
+        <v>0.2163430585580168</v>
       </c>
       <c r="W84">
-        <v>0.1146535321622646</v>
+        <v>0.1150408390036831</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8759255541617266</v>
+        <v>0.8653722342320672</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1572337025297454</v>
+        <v>0.1582437025297453</v>
       </c>
       <c r="C85">
-        <v>-38.12596818933132</v>
+        <v>-40.43836597582293</v>
       </c>
       <c r="D85">
-        <v>85.54603181066869</v>
+        <v>84.77763402417709</v>
       </c>
       <c r="E85">
-        <v>90.15200000000002</v>
+        <v>91.69600000000003</v>
       </c>
       <c r="F85">
-        <v>128.152</v>
+        <v>129.696</v>
       </c>
       <c r="G85">
         <v>4.48</v>
@@ -8251,37 +8251,37 @@
         <v>16.28</v>
       </c>
       <c r="M85">
-        <v>18.81271360000001</v>
+        <v>19.03937280000001</v>
       </c>
       <c r="N85">
-        <v>-2.532713600000005</v>
+        <v>-2.759372800000005</v>
       </c>
       <c r="O85">
-        <v>-0.6331784000000011</v>
+        <v>-0.6898432000000012</v>
       </c>
       <c r="P85">
-        <v>-1.899535200000003</v>
+        <v>-2.069529600000004</v>
       </c>
       <c r="Q85">
-        <v>1.520464799999997</v>
+        <v>1.350470399999996</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3632341538628727</v>
+        <v>0.3830737884793023</v>
       </c>
       <c r="T85">
-        <v>4.910605404100149</v>
+        <v>5.21751824185641</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2163430585580168</v>
+        <v>0.2137675459561356</v>
       </c>
       <c r="W85">
-        <v>0.1150408390036831</v>
+        <v>0.1154189242536393</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8653722342320672</v>
+        <v>0.8550701838245426</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1582437025297454</v>
+        <v>0.1592537025297454</v>
       </c>
       <c r="C86">
-        <v>-40.43836597582292</v>
+        <v>-42.73708273213124</v>
       </c>
       <c r="D86">
-        <v>84.77763402417708</v>
+        <v>84.02291726786876</v>
       </c>
       <c r="E86">
-        <v>91.696</v>
+        <v>93.24000000000001</v>
       </c>
       <c r="F86">
-        <v>129.696</v>
+        <v>131.24</v>
       </c>
       <c r="G86">
         <v>4.48</v>
@@ -8333,37 +8333,37 @@
         <v>16.28</v>
       </c>
       <c r="M86">
-        <v>19.0393728</v>
+        <v>19.266032</v>
       </c>
       <c r="N86">
-        <v>-2.759372800000001</v>
+        <v>-2.986032000000002</v>
       </c>
       <c r="O86">
-        <v>-0.6898432000000003</v>
+        <v>-0.7465080000000004</v>
       </c>
       <c r="P86">
-        <v>-2.069529600000001</v>
+        <v>-2.239524000000001</v>
       </c>
       <c r="Q86">
-        <v>1.350470399999999</v>
+        <v>1.180475999999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3830737884793021</v>
+        <v>0.4055587077112556</v>
       </c>
       <c r="T86">
-        <v>5.217518241856406</v>
+        <v>5.5653527913135</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2137675459561357</v>
+        <v>0.2112526336507694</v>
       </c>
       <c r="W86">
-        <v>0.1154189242536393</v>
+        <v>0.1157881133800671</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8550701838245427</v>
+        <v>0.8450105346030775</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1592537025297454</v>
+        <v>0.1602637025297454</v>
       </c>
       <c r="C87">
-        <v>-42.73708273213124</v>
+        <v>-45.02248061255095</v>
       </c>
       <c r="D87">
-        <v>84.02291726786876</v>
+        <v>83.28151938744904</v>
       </c>
       <c r="E87">
-        <v>93.24000000000001</v>
+        <v>94.78399999999999</v>
       </c>
       <c r="F87">
-        <v>131.24</v>
+        <v>132.784</v>
       </c>
       <c r="G87">
         <v>4.48</v>
@@ -8415,37 +8415,37 @@
         <v>16.28</v>
       </c>
       <c r="M87">
-        <v>19.266032</v>
+        <v>19.4926912</v>
       </c>
       <c r="N87">
-        <v>-2.986032000000002</v>
+        <v>-3.212691199999998</v>
       </c>
       <c r="O87">
-        <v>-0.7465080000000004</v>
+        <v>-0.8031727999999996</v>
       </c>
       <c r="P87">
-        <v>-2.239524000000001</v>
+        <v>-2.409518399999999</v>
       </c>
       <c r="Q87">
-        <v>1.180475999999999</v>
+        <v>1.010481600000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4055587077112556</v>
+        <v>0.4312557582620596</v>
       </c>
       <c r="T87">
-        <v>5.5653527913135</v>
+        <v>5.962877990693036</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2112526336507694</v>
+        <v>0.208796207678086</v>
       </c>
       <c r="W87">
-        <v>0.1157881133800671</v>
+        <v>0.116148716712857</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8450105346030775</v>
+        <v>0.8351848307123442</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1602637025297454</v>
+        <v>0.1612737025297453</v>
       </c>
       <c r="C88">
-        <v>-45.02248061255095</v>
+        <v>-47.29490910093041</v>
       </c>
       <c r="D88">
-        <v>83.28151938744904</v>
+        <v>82.55309089906959</v>
       </c>
       <c r="E88">
-        <v>94.78399999999999</v>
+        <v>96.328</v>
       </c>
       <c r="F88">
-        <v>132.784</v>
+        <v>134.328</v>
       </c>
       <c r="G88">
         <v>4.48</v>
@@ -8497,37 +8497,37 @@
         <v>16.28</v>
       </c>
       <c r="M88">
-        <v>19.4926912</v>
+        <v>19.7193504</v>
       </c>
       <c r="N88">
-        <v>-3.212691199999998</v>
+        <v>-3.439350400000002</v>
       </c>
       <c r="O88">
-        <v>-0.8031727999999996</v>
+        <v>-0.8598376000000005</v>
       </c>
       <c r="P88">
-        <v>-2.409518399999999</v>
+        <v>-2.579512800000002</v>
       </c>
       <c r="Q88">
-        <v>1.010481600000001</v>
+        <v>0.8404871999999983</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4312557582620596</v>
+        <v>0.4609062012052949</v>
       </c>
       <c r="T88">
-        <v>5.962877990693036</v>
+        <v>6.421560913054038</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.208796207678086</v>
+        <v>0.2063962512679931</v>
       </c>
       <c r="W88">
-        <v>0.116148716712857</v>
+        <v>0.1165010303138586</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8351848307123442</v>
+        <v>0.8255850050719723</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1612737025297453</v>
+        <v>0.1622837025297453</v>
       </c>
       <c r="C89">
-        <v>-47.29490910093041</v>
+        <v>-49.55470555998244</v>
       </c>
       <c r="D89">
-        <v>82.55309089906959</v>
+        <v>81.83729444001757</v>
       </c>
       <c r="E89">
-        <v>96.328</v>
+        <v>97.87200000000001</v>
       </c>
       <c r="F89">
-        <v>134.328</v>
+        <v>135.872</v>
       </c>
       <c r="G89">
         <v>4.48</v>
@@ -8579,37 +8579,37 @@
         <v>16.28</v>
       </c>
       <c r="M89">
-        <v>19.7193504</v>
+        <v>19.9460096</v>
       </c>
       <c r="N89">
-        <v>-3.439350400000002</v>
+        <v>-3.666009600000002</v>
       </c>
       <c r="O89">
-        <v>-0.8598376000000005</v>
+        <v>-0.9165024000000006</v>
       </c>
       <c r="P89">
-        <v>-2.579512800000002</v>
+        <v>-2.749507200000002</v>
       </c>
       <c r="Q89">
-        <v>0.8404871999999983</v>
+        <v>0.6704927999999981</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4609062012052949</v>
+        <v>0.4954983846390696</v>
       </c>
       <c r="T89">
-        <v>6.421560913054038</v>
+        <v>6.956690989141876</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2063962512679931</v>
+        <v>0.2040508393217659</v>
       </c>
       <c r="W89">
-        <v>0.1165010303138586</v>
+        <v>0.1168453367875648</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8255850050719723</v>
+        <v>0.8162033572870635</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1622837025297453</v>
+        <v>0.1632937025297453</v>
       </c>
       <c r="C90">
-        <v>-49.55470555998244</v>
+        <v>-51.8021957522631</v>
       </c>
       <c r="D90">
-        <v>81.83729444001757</v>
+        <v>81.13380424773689</v>
       </c>
       <c r="E90">
-        <v>97.87200000000001</v>
+        <v>99.416</v>
       </c>
       <c r="F90">
-        <v>135.872</v>
+        <v>137.416</v>
       </c>
       <c r="G90">
         <v>4.48</v>
@@ -8661,37 +8661,37 @@
         <v>16.28</v>
       </c>
       <c r="M90">
-        <v>19.9460096</v>
+        <v>20.1726688</v>
       </c>
       <c r="N90">
-        <v>-3.666009600000002</v>
+        <v>-3.892668799999999</v>
       </c>
       <c r="O90">
-        <v>-0.9165024000000006</v>
+        <v>-0.9731671999999998</v>
       </c>
       <c r="P90">
-        <v>-2.749507200000002</v>
+        <v>-2.919501599999999</v>
       </c>
       <c r="Q90">
-        <v>0.6704927999999981</v>
+        <v>0.5004984000000006</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4954983846390696</v>
+        <v>0.536380055969894</v>
       </c>
       <c r="T90">
-        <v>6.956690989141876</v>
+        <v>7.589117442700228</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.2040508393217659</v>
+        <v>0.2017581332619708</v>
       </c>
       <c r="W90">
-        <v>0.1168453367875648</v>
+        <v>0.1171819060371427</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8162033572870635</v>
+        <v>0.8070325330478831</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1632937025297453</v>
+        <v>0.2160799136724226</v>
       </c>
       <c r="C91">
-        <v>-51.8021957522631</v>
+        <v>-78.49740724552623</v>
       </c>
       <c r="D91">
-        <v>81.13380424773689</v>
+        <v>55.98259275447378</v>
       </c>
       <c r="E91">
-        <v>99.416</v>
+        <v>100.96</v>
       </c>
       <c r="F91">
-        <v>137.416</v>
+        <v>138.96</v>
       </c>
       <c r="G91">
         <v>4.48</v>
@@ -8743,45 +8743,45 @@
         <v>16.28</v>
       </c>
       <c r="M91">
-        <v>20.1726688</v>
+        <v>27.903168</v>
       </c>
       <c r="N91">
-        <v>-3.892668799999999</v>
+        <v>-11.623168</v>
       </c>
       <c r="O91">
-        <v>-0.9731671999999998</v>
+        <v>-2.905792</v>
       </c>
       <c r="P91">
-        <v>-2.919501599999999</v>
+        <v>-8.717376</v>
       </c>
       <c r="Q91">
-        <v>0.5004984000000006</v>
+        <v>-5.297376</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.536380055969894</v>
+        <v>0.6172001729936564</v>
       </c>
       <c r="T91">
-        <v>7.589117442700228</v>
+        <v>8.839378949180526</v>
       </c>
       <c r="U91">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.2017581332619708</v>
+        <v>0.1458615738542663</v>
       </c>
       <c r="W91">
-        <v>0.1171819060371427</v>
+        <v>0.1715109959700633</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y91">
-        <v>0.8070325330478831</v>
+        <v>0.5834462954170652</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2160799136724226</v>
+        <v>0.2176299136724226</v>
       </c>
       <c r="C92">
-        <v>-78.49740724552623</v>
+        <v>-80.54640091580684</v>
       </c>
       <c r="D92">
-        <v>55.98259275447378</v>
+        <v>55.47759908419318</v>
       </c>
       <c r="E92">
-        <v>100.96</v>
+        <v>102.504</v>
       </c>
       <c r="F92">
-        <v>138.96</v>
+        <v>140.504</v>
       </c>
       <c r="G92">
         <v>4.48</v>
@@ -8825,37 +8825,37 @@
         <v>16.28</v>
       </c>
       <c r="M92">
-        <v>27.903168</v>
+        <v>28.21320320000001</v>
       </c>
       <c r="N92">
-        <v>-11.623168</v>
+        <v>-11.9332032</v>
       </c>
       <c r="O92">
-        <v>-2.905792</v>
+        <v>-2.983300800000001</v>
       </c>
       <c r="P92">
-        <v>-8.717376</v>
+        <v>-8.949902400000003</v>
       </c>
       <c r="Q92">
-        <v>-5.297376</v>
+        <v>-5.529902400000003</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6172001729936564</v>
+        <v>0.6806890811040627</v>
       </c>
       <c r="T92">
-        <v>8.839378949180526</v>
+        <v>9.821532165756141</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1458615738542663</v>
+        <v>0.1442586994163073</v>
       </c>
       <c r="W92">
-        <v>0.1715109959700633</v>
+        <v>0.1718328531572055</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5834462954170652</v>
+        <v>0.5770347976652292</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2176299136724226</v>
+        <v>0.2191799136724227</v>
       </c>
       <c r="C93">
-        <v>-80.54640091580684</v>
+        <v>-82.58636539496193</v>
       </c>
       <c r="D93">
-        <v>55.47759908419318</v>
+        <v>54.98163460503807</v>
       </c>
       <c r="E93">
-        <v>102.504</v>
+        <v>104.048</v>
       </c>
       <c r="F93">
-        <v>140.504</v>
+        <v>142.048</v>
       </c>
       <c r="G93">
         <v>4.48</v>
@@ -8907,37 +8907,37 @@
         <v>16.28</v>
       </c>
       <c r="M93">
-        <v>28.21320320000001</v>
+        <v>28.5232384</v>
       </c>
       <c r="N93">
-        <v>-11.9332032</v>
+        <v>-12.2432384</v>
       </c>
       <c r="O93">
-        <v>-2.983300800000001</v>
+        <v>-3.0608096</v>
       </c>
       <c r="P93">
-        <v>-8.949902400000003</v>
+        <v>-9.1824288</v>
       </c>
       <c r="Q93">
-        <v>-5.529902400000003</v>
+        <v>-5.7624288</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6806890811040627</v>
+        <v>0.7600502162420709</v>
       </c>
       <c r="T93">
-        <v>9.821532165756141</v>
+        <v>11.04922368647566</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1442586994163073</v>
+        <v>0.1426906700748257</v>
       </c>
       <c r="W93">
-        <v>0.1718328531572055</v>
+        <v>0.172147713448975</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5770347976652292</v>
+        <v>0.5707626802993029</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2191799136724227</v>
+        <v>0.2207299136724226</v>
       </c>
       <c r="C94">
-        <v>-82.58636539496193</v>
+        <v>-84.61754069762283</v>
       </c>
       <c r="D94">
-        <v>54.98163460503807</v>
+        <v>54.49445930237718</v>
       </c>
       <c r="E94">
-        <v>104.048</v>
+        <v>105.592</v>
       </c>
       <c r="F94">
-        <v>142.048</v>
+        <v>143.592</v>
       </c>
       <c r="G94">
         <v>4.48</v>
@@ -8989,37 +8989,37 @@
         <v>16.28</v>
       </c>
       <c r="M94">
-        <v>28.5232384</v>
+        <v>28.8332736</v>
       </c>
       <c r="N94">
-        <v>-12.2432384</v>
+        <v>-12.5532736</v>
       </c>
       <c r="O94">
-        <v>-3.0608096</v>
+        <v>-3.1383184</v>
       </c>
       <c r="P94">
-        <v>-9.1824288</v>
+        <v>-9.414955200000001</v>
       </c>
       <c r="Q94">
-        <v>-5.7624288</v>
+        <v>-5.994955200000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7600502162420709</v>
+        <v>0.8620859614195095</v>
       </c>
       <c r="T94">
-        <v>11.04922368647566</v>
+        <v>12.62768421311504</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1426906700748257</v>
+        <v>0.1411563617944513</v>
       </c>
       <c r="W94">
-        <v>0.172147713448975</v>
+        <v>0.1724558025516742</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5707626802993029</v>
+        <v>0.5646254471778051</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2207299136724226</v>
+        <v>0.2222799136724226</v>
       </c>
       <c r="C95">
-        <v>-84.61754069762283</v>
+        <v>-86.6401584063524</v>
       </c>
       <c r="D95">
-        <v>54.49445930237718</v>
+        <v>54.01584159364762</v>
       </c>
       <c r="E95">
-        <v>105.592</v>
+        <v>107.136</v>
       </c>
       <c r="F95">
-        <v>143.592</v>
+        <v>145.136</v>
       </c>
       <c r="G95">
         <v>4.48</v>
@@ -9071,37 +9071,37 @@
         <v>16.28</v>
       </c>
       <c r="M95">
-        <v>28.8332736</v>
+        <v>29.14330880000001</v>
       </c>
       <c r="N95">
-        <v>-12.5532736</v>
+        <v>-12.86330880000001</v>
       </c>
       <c r="O95">
-        <v>-3.1383184</v>
+        <v>-3.215827200000001</v>
       </c>
       <c r="P95">
-        <v>-9.414955200000001</v>
+        <v>-9.647481600000004</v>
       </c>
       <c r="Q95">
-        <v>-5.994955200000001</v>
+        <v>-6.227481600000004</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8620859614195095</v>
+        <v>0.9981336216560949</v>
       </c>
       <c r="T95">
-        <v>12.62768421311504</v>
+        <v>14.73229824863422</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1411563617944513</v>
+        <v>0.139654698371106</v>
       </c>
       <c r="W95">
-        <v>0.1724558025516742</v>
+        <v>0.1727573365670819</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5646254471778051</v>
+        <v>0.558618793484424</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2222799136724226</v>
+        <v>0.2238299136724227</v>
       </c>
       <c r="C96">
-        <v>-86.6401584063524</v>
+        <v>-88.65444203870987</v>
       </c>
       <c r="D96">
-        <v>54.01584159364762</v>
+        <v>53.54555796129014</v>
       </c>
       <c r="E96">
-        <v>107.136</v>
+        <v>108.68</v>
       </c>
       <c r="F96">
-        <v>145.136</v>
+        <v>146.68</v>
       </c>
       <c r="G96">
         <v>4.48</v>
@@ -9153,37 +9153,37 @@
         <v>16.28</v>
       </c>
       <c r="M96">
-        <v>29.14330880000001</v>
+        <v>29.453344</v>
       </c>
       <c r="N96">
-        <v>-12.86330880000001</v>
+        <v>-13.173344</v>
       </c>
       <c r="O96">
-        <v>-3.215827200000001</v>
+        <v>-3.293336</v>
       </c>
       <c r="P96">
-        <v>-9.647481600000004</v>
+        <v>-9.880008</v>
       </c>
       <c r="Q96">
-        <v>-6.227481600000004</v>
+        <v>-6.460008</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9981336216560949</v>
+        <v>1.188600345987314</v>
       </c>
       <c r="T96">
-        <v>14.73229824863422</v>
+        <v>17.67875789836108</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.139654698371106</v>
+        <v>0.1381846489145681</v>
       </c>
       <c r="W96">
-        <v>0.1727573365670819</v>
+        <v>0.1730525224979547</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.558618793484424</v>
+        <v>0.5527385956582723</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2238299136724227</v>
+        <v>0.2253799136724227</v>
       </c>
       <c r="C97">
-        <v>-88.65444203870987</v>
+        <v>-90.66060739530647</v>
       </c>
       <c r="D97">
-        <v>53.54555796129014</v>
+        <v>53.08339260469355</v>
       </c>
       <c r="E97">
-        <v>108.68</v>
+        <v>110.224</v>
       </c>
       <c r="F97">
-        <v>146.68</v>
+        <v>148.224</v>
       </c>
       <c r="G97">
         <v>4.48</v>
@@ -9235,37 +9235,37 @@
         <v>16.28</v>
       </c>
       <c r="M97">
-        <v>29.453344</v>
+        <v>29.7633792</v>
       </c>
       <c r="N97">
-        <v>-13.173344</v>
+        <v>-13.4833792</v>
       </c>
       <c r="O97">
-        <v>-3.293336</v>
+        <v>-3.3708448</v>
       </c>
       <c r="P97">
-        <v>-9.880008</v>
+        <v>-10.1125344</v>
       </c>
       <c r="Q97">
-        <v>-6.460008</v>
+        <v>-6.692534400000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.188600345987314</v>
+        <v>1.474300432484144</v>
       </c>
       <c r="T97">
-        <v>17.67875789836108</v>
+        <v>22.09844737295135</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1381846489145681</v>
+        <v>0.1367452254883746</v>
       </c>
       <c r="W97">
-        <v>0.1730525224979547</v>
+        <v>0.1733415587219344</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5527385956582723</v>
+        <v>0.5469809019534986</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2253799136724227</v>
+        <v>0.2269299136724226</v>
       </c>
       <c r="C98">
-        <v>-90.66060739530644</v>
+        <v>-92.65886288999009</v>
       </c>
       <c r="D98">
-        <v>53.08339260469355</v>
+        <v>52.62913711000991</v>
       </c>
       <c r="E98">
-        <v>110.224</v>
+        <v>111.768</v>
       </c>
       <c r="F98">
-        <v>148.224</v>
+        <v>149.768</v>
       </c>
       <c r="G98">
         <v>4.48</v>
@@ -9317,37 +9317,37 @@
         <v>16.28</v>
       </c>
       <c r="M98">
-        <v>29.7633792</v>
+        <v>30.0734144</v>
       </c>
       <c r="N98">
-        <v>-13.4833792</v>
+        <v>-13.7934144</v>
       </c>
       <c r="O98">
-        <v>-3.3708448</v>
+        <v>-3.4483536</v>
       </c>
       <c r="P98">
-        <v>-10.1125344</v>
+        <v>-10.3450608</v>
       </c>
       <c r="Q98">
-        <v>-6.692534399999998</v>
+        <v>-6.925060799999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.47430043248414</v>
+        <v>1.950467243312186</v>
       </c>
       <c r="T98">
-        <v>22.09844737295129</v>
+        <v>29.46459649726839</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1367452254883747</v>
+        <v>0.135335480895711</v>
       </c>
       <c r="W98">
-        <v>0.1733415587219344</v>
+        <v>0.1736246354361412</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5469809019534987</v>
+        <v>0.5413419235828441</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2269299136724226</v>
+        <v>0.2284799136724226</v>
       </c>
       <c r="C99">
-        <v>-92.65886288999009</v>
+        <v>-94.64940986322108</v>
       </c>
       <c r="D99">
-        <v>52.62913711000991</v>
+        <v>52.18259013677893</v>
       </c>
       <c r="E99">
-        <v>111.768</v>
+        <v>113.312</v>
       </c>
       <c r="F99">
-        <v>149.768</v>
+        <v>151.312</v>
       </c>
       <c r="G99">
         <v>4.48</v>
@@ -9399,37 +9399,37 @@
         <v>16.28</v>
       </c>
       <c r="M99">
-        <v>30.0734144</v>
+        <v>30.3834496</v>
       </c>
       <c r="N99">
-        <v>-13.7934144</v>
+        <v>-14.1034496</v>
       </c>
       <c r="O99">
-        <v>-3.4483536</v>
+        <v>-3.5258624</v>
       </c>
       <c r="P99">
-        <v>-10.3450608</v>
+        <v>-10.5775872</v>
       </c>
       <c r="Q99">
-        <v>-6.925060799999999</v>
+        <v>-7.1575872</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.950467243312186</v>
+        <v>2.902800864968279</v>
       </c>
       <c r="T99">
-        <v>29.46459649726839</v>
+        <v>44.19689474590259</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.135335480895711</v>
+        <v>0.1339545066008568</v>
       </c>
       <c r="W99">
-        <v>0.1736246354361412</v>
+        <v>0.173901935074548</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5413419235828441</v>
+        <v>0.5358180264034271</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2284799136724226</v>
+        <v>0.2300299136724226</v>
       </c>
       <c r="C100">
-        <v>-94.64940986322108</v>
+        <v>-96.63244287962809</v>
       </c>
       <c r="D100">
-        <v>52.18259013677893</v>
+        <v>51.74355712037191</v>
       </c>
       <c r="E100">
-        <v>113.312</v>
+        <v>114.856</v>
       </c>
       <c r="F100">
-        <v>151.312</v>
+        <v>152.856</v>
       </c>
       <c r="G100">
         <v>4.48</v>
@@ -9481,37 +9481,37 @@
         <v>16.28</v>
       </c>
       <c r="M100">
-        <v>30.3834496</v>
+        <v>30.6934848</v>
       </c>
       <c r="N100">
-        <v>-14.1034496</v>
+        <v>-14.4134848</v>
       </c>
       <c r="O100">
-        <v>-3.5258624</v>
+        <v>-3.6033712</v>
       </c>
       <c r="P100">
-        <v>-10.5775872</v>
+        <v>-10.8101136</v>
       </c>
       <c r="Q100">
-        <v>-7.1575872</v>
+        <v>-7.390113599999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.902800864968279</v>
+        <v>5.759801729936559</v>
       </c>
       <c r="T100">
-        <v>44.19689474590259</v>
+        <v>88.39378949180518</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1339545066008568</v>
+        <v>0.1326014307766057</v>
       </c>
       <c r="W100">
-        <v>0.173901935074548</v>
+        <v>0.1741736327000576</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5358180264034271</v>
+        <v>0.530405723106423</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2300299136724226</v>
-      </c>
-      <c r="C101">
-        <v>-96.63244287962809</v>
-      </c>
-      <c r="D101">
-        <v>51.74355712037191</v>
-      </c>
-      <c r="E101">
-        <v>114.856</v>
-      </c>
-      <c r="F101">
-        <v>152.856</v>
-      </c>
-      <c r="G101">
-        <v>4.48</v>
-      </c>
-      <c r="H101">
-        <v>116.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>19.7</v>
-      </c>
-      <c r="K101">
-        <v>3.42</v>
-      </c>
-      <c r="L101">
-        <v>16.28</v>
-      </c>
-      <c r="M101">
-        <v>30.6934848</v>
-      </c>
-      <c r="N101">
-        <v>-14.4134848</v>
-      </c>
-      <c r="O101">
-        <v>-3.6033712</v>
-      </c>
-      <c r="P101">
-        <v>-10.8101136</v>
-      </c>
-      <c r="Q101">
-        <v>-7.390113599999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.759801729936559</v>
-      </c>
-      <c r="T101">
-        <v>88.39378949180518</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1326014307766057</v>
-      </c>
-      <c r="W101">
-        <v>0.1741736327000576</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.530405723106423</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
